--- a/BEDEL(2).xlsx
+++ b/BEDEL(2).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760" activeTab="3"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="MED LEMIN (2)" sheetId="4" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="30">
   <si>
     <t>Description</t>
   </si>
@@ -112,6 +112,9 @@
   </si>
   <si>
     <t>x</t>
+  </si>
+  <si>
+    <t>CONX</t>
   </si>
 </sst>
 </file>
@@ -242,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -361,6 +364,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -376,10 +382,10 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -694,40 +700,40 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="17.5703125" defaultRowHeight="24" customHeight="1"/>
   <sheetData>
     <row r="2" spans="2:8" ht="24" customHeight="1">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="41">
+      <c r="C2" s="42">
         <f>SUM(D5:D14)</f>
         <v>700</v>
       </c>
-      <c r="D2" s="41"/>
-      <c r="F2" s="42">
+      <c r="D2" s="42"/>
+      <c r="F2" s="43">
         <v>9</v>
       </c>
-      <c r="G2" s="41">
+      <c r="G2" s="42">
         <f>SUM(H5:H35)</f>
         <v>2175</v>
       </c>
-      <c r="H2" s="41"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="2:8" ht="24" customHeight="1">
-      <c r="B3" s="40"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
     </row>
     <row r="4" spans="2:8" ht="24" customHeight="1">
-      <c r="B4" s="40"/>
+      <c r="B4" s="41"/>
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="42"/>
+      <c r="F4" s="43"/>
       <c r="G4" s="8" t="s">
         <v>0</v>
       </c>
@@ -1170,20 +1176,20 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="17.5703125" defaultRowHeight="24" customHeight="1"/>
   <sheetData>
     <row r="2" spans="1:4" ht="24" customHeight="1">
-      <c r="B2" s="42"/>
-      <c r="C2" s="41">
+      <c r="B2" s="43"/>
+      <c r="C2" s="42">
         <f>SUM(D5:D31)</f>
         <v>2400</v>
       </c>
-      <c r="D2" s="41"/>
+      <c r="D2" s="42"/>
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
-      <c r="B3" s="42"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
     </row>
     <row r="4" spans="1:4" ht="24" customHeight="1">
-      <c r="B4" s="42"/>
+      <c r="B4" s="43"/>
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
@@ -1395,58 +1401,58 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="24" customHeight="1">
-      <c r="B2" s="43">
+      <c r="B2" s="44">
         <v>7</v>
       </c>
-      <c r="C2" s="44">
+      <c r="C2" s="45">
         <f>SUM(D5:D7)</f>
         <v>8500</v>
       </c>
-      <c r="D2" s="44"/>
-      <c r="F2" s="43">
+      <c r="D2" s="45"/>
+      <c r="F2" s="44">
         <v>8</v>
       </c>
-      <c r="G2" s="44">
+      <c r="G2" s="45">
         <f>SUM(H5:H7)</f>
         <v>8500</v>
       </c>
-      <c r="H2" s="44"/>
-      <c r="J2" s="43">
+      <c r="H2" s="45"/>
+      <c r="J2" s="44">
         <v>9</v>
       </c>
-      <c r="K2" s="44">
+      <c r="K2" s="45">
         <f>SUM(L5:L7)</f>
         <v>1500</v>
       </c>
-      <c r="L2" s="44"/>
+      <c r="L2" s="45"/>
     </row>
     <row r="3" spans="2:12" ht="24" customHeight="1">
-      <c r="B3" s="43"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
     </row>
     <row r="4" spans="2:12" ht="24" customHeight="1">
-      <c r="B4" s="43"/>
+      <c r="B4" s="44"/>
       <c r="C4" s="9" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="43"/>
+      <c r="F4" s="44"/>
       <c r="G4" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="J4" s="43"/>
+      <c r="J4" s="44"/>
       <c r="K4" s="9" t="s">
         <v>0</v>
       </c>
@@ -1517,56 +1523,56 @@
       <c r="F9" s="10"/>
     </row>
     <row r="10" spans="2:12" ht="24" customHeight="1">
-      <c r="B10" s="43">
+      <c r="B10" s="44">
         <v>10</v>
       </c>
-      <c r="C10" s="44">
+      <c r="C10" s="45">
         <f>SUM(D13:D39)</f>
         <v>8500</v>
       </c>
-      <c r="D10" s="44"/>
-      <c r="F10" s="43">
+      <c r="D10" s="45"/>
+      <c r="F10" s="44">
         <v>11</v>
       </c>
-      <c r="G10" s="44">
+      <c r="G10" s="45">
         <f>SUM(H13:H45)</f>
         <v>8500</v>
       </c>
-      <c r="H10" s="44"/>
-      <c r="J10" s="43"/>
-      <c r="K10" s="44">
+      <c r="H10" s="45"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="45">
         <f>SUM(L13:L44)</f>
         <v>4400</v>
       </c>
-      <c r="L10" s="44"/>
+      <c r="L10" s="45"/>
     </row>
     <row r="11" spans="2:12" ht="24" customHeight="1">
-      <c r="B11" s="43"/>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
-      <c r="J11" s="43"/>
-      <c r="K11" s="44"/>
-      <c r="L11" s="44"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="45"/>
+      <c r="J11" s="44"/>
+      <c r="K11" s="45"/>
+      <c r="L11" s="45"/>
     </row>
     <row r="12" spans="2:12" ht="24" customHeight="1">
-      <c r="B12" s="43"/>
+      <c r="B12" s="44"/>
       <c r="C12" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D12" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F12" s="43"/>
+      <c r="F12" s="44"/>
       <c r="G12" s="16" t="s">
         <v>0</v>
       </c>
       <c r="H12" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="J12" s="43"/>
+      <c r="J12" s="44"/>
       <c r="K12" s="19" t="s">
         <v>0</v>
       </c>
@@ -2177,7 +2183,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:28" ht="24" customHeight="1">
-      <c r="B2" s="45">
+      <c r="B2" s="47">
         <v>6</v>
       </c>
       <c r="C2" s="46">
@@ -2185,7 +2191,7 @@
         <v>13000</v>
       </c>
       <c r="D2" s="46"/>
-      <c r="F2" s="45">
+      <c r="F2" s="47">
         <v>7</v>
       </c>
       <c r="G2" s="46">
@@ -2193,7 +2199,7 @@
         <v>13000</v>
       </c>
       <c r="H2" s="46"/>
-      <c r="J2" s="45">
+      <c r="J2" s="47">
         <v>8</v>
       </c>
       <c r="K2" s="46">
@@ -2201,7 +2207,7 @@
         <v>13000</v>
       </c>
       <c r="L2" s="46"/>
-      <c r="N2" s="45">
+      <c r="N2" s="47">
         <v>9</v>
       </c>
       <c r="O2" s="46">
@@ -2209,7 +2215,7 @@
         <v>13000</v>
       </c>
       <c r="P2" s="46"/>
-      <c r="R2" s="45">
+      <c r="R2" s="47">
         <v>11</v>
       </c>
       <c r="S2" s="46">
@@ -2217,7 +2223,7 @@
         <v>13000</v>
       </c>
       <c r="T2" s="46"/>
-      <c r="V2" s="45">
+      <c r="V2" s="47">
         <v>12</v>
       </c>
       <c r="W2" s="46">
@@ -2225,82 +2231,82 @@
         <v>16500</v>
       </c>
       <c r="X2" s="46"/>
-      <c r="Z2" s="45">
+      <c r="Z2" s="47">
         <v>1</v>
       </c>
       <c r="AA2" s="46">
         <f>SUM(AB5:AB35)</f>
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="AB2" s="46"/>
     </row>
     <row r="3" spans="2:28" ht="24" customHeight="1">
-      <c r="B3" s="45"/>
+      <c r="B3" s="47"/>
       <c r="C3" s="46"/>
       <c r="D3" s="46"/>
-      <c r="F3" s="45"/>
+      <c r="F3" s="47"/>
       <c r="G3" s="46"/>
       <c r="H3" s="46"/>
-      <c r="J3" s="45"/>
+      <c r="J3" s="47"/>
       <c r="K3" s="46"/>
       <c r="L3" s="46"/>
-      <c r="N3" s="45"/>
+      <c r="N3" s="47"/>
       <c r="O3" s="46"/>
       <c r="P3" s="46"/>
-      <c r="R3" s="45"/>
+      <c r="R3" s="47"/>
       <c r="S3" s="46"/>
       <c r="T3" s="46"/>
-      <c r="V3" s="45"/>
+      <c r="V3" s="47"/>
       <c r="W3" s="46"/>
       <c r="X3" s="46"/>
-      <c r="Z3" s="45"/>
+      <c r="Z3" s="47"/>
       <c r="AA3" s="46"/>
       <c r="AB3" s="46"/>
     </row>
     <row r="4" spans="2:28" ht="24" customHeight="1">
-      <c r="B4" s="45"/>
+      <c r="B4" s="47"/>
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="45"/>
+      <c r="F4" s="47"/>
       <c r="G4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="J4" s="45"/>
+      <c r="J4" s="47"/>
       <c r="K4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="N4" s="45"/>
+      <c r="N4" s="47"/>
       <c r="O4" s="6" t="s">
         <v>0</v>
       </c>
       <c r="P4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="R4" s="45"/>
+      <c r="R4" s="47"/>
       <c r="S4" s="18" t="s">
         <v>0</v>
       </c>
       <c r="T4" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="V4" s="45"/>
+      <c r="V4" s="47"/>
       <c r="W4" s="20" t="s">
         <v>0</v>
       </c>
       <c r="X4" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="Z4" s="45"/>
+      <c r="Z4" s="47"/>
       <c r="AA4" s="23" t="s">
         <v>0</v>
       </c>
@@ -2360,6 +2366,9 @@
       <c r="Z5" s="1">
         <v>46018</v>
       </c>
+      <c r="AA5" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="AB5" s="2">
         <v>100</v>
       </c>
@@ -2419,6 +2428,9 @@
       <c r="Z6" s="1">
         <v>46019</v>
       </c>
+      <c r="AA6" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="AB6" s="2">
         <v>100</v>
       </c>
@@ -2478,6 +2490,9 @@
       <c r="Z7" s="1">
         <v>46020</v>
       </c>
+      <c r="AA7" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="AB7" s="2">
         <v>100</v>
       </c>
@@ -2537,6 +2552,9 @@
       <c r="Z8" s="1">
         <v>46021</v>
       </c>
+      <c r="AA8" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="AB8" s="2">
         <v>100</v>
       </c>
@@ -2587,6 +2605,9 @@
       <c r="Z9" s="1">
         <v>46022</v>
       </c>
+      <c r="AA9" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="AB9" s="2">
         <v>100</v>
       </c>
@@ -2637,6 +2658,9 @@
       <c r="Z10" s="1">
         <v>46023</v>
       </c>
+      <c r="AA10" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="AB10" s="2">
         <v>100</v>
       </c>
@@ -2666,7 +2690,7 @@
       <c r="L11" s="2">
         <v>100</v>
       </c>
-      <c r="N11" s="45">
+      <c r="N11" s="47">
         <v>10</v>
       </c>
       <c r="O11" s="46">
@@ -2695,6 +2719,9 @@
       <c r="Z11" s="1">
         <v>46024</v>
       </c>
+      <c r="AA11" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="AB11" s="2">
         <v>100</v>
       </c>
@@ -2724,7 +2751,7 @@
       <c r="L12" s="2">
         <v>100</v>
       </c>
-      <c r="N12" s="45"/>
+      <c r="N12" s="47"/>
       <c r="O12" s="46"/>
       <c r="P12" s="46"/>
       <c r="R12" s="1">
@@ -2748,6 +2775,9 @@
       <c r="Z12" s="1">
         <v>46025</v>
       </c>
+      <c r="AA12" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="AB12" s="2">
         <v>100</v>
       </c>
@@ -2777,7 +2807,7 @@
       <c r="L13" s="2">
         <v>100</v>
       </c>
-      <c r="N13" s="45"/>
+      <c r="N13" s="47"/>
       <c r="O13" s="14" t="s">
         <v>0</v>
       </c>
@@ -2804,6 +2834,9 @@
       </c>
       <c r="Z13" s="1">
         <v>46026</v>
+      </c>
+      <c r="AA13" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="AB13" s="2">
         <v>100</v>
@@ -2864,6 +2897,9 @@
       <c r="Z14" s="1">
         <v>46027</v>
       </c>
+      <c r="AA14" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="AB14" s="2">
         <v>100</v>
       </c>
@@ -2923,6 +2959,9 @@
       <c r="Z15" s="1">
         <v>46028</v>
       </c>
+      <c r="AA15" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="AB15" s="2">
         <v>100</v>
       </c>
@@ -2982,6 +3021,9 @@
       <c r="Z16" s="1">
         <v>46029</v>
       </c>
+      <c r="AA16" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="AB16" s="2">
         <v>200</v>
       </c>
@@ -3041,6 +3083,9 @@
       <c r="Z17" s="1">
         <v>46030</v>
       </c>
+      <c r="AA17" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="AB17" s="2">
         <v>100</v>
       </c>
@@ -3100,6 +3145,9 @@
       <c r="Z18" s="1">
         <v>46031</v>
       </c>
+      <c r="AA18" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="AB18" s="2">
         <v>100</v>
       </c>
@@ -3159,6 +3207,9 @@
       <c r="Z19" s="1">
         <v>46032</v>
       </c>
+      <c r="AA19" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="AB19" s="2">
         <v>200</v>
       </c>
@@ -3218,6 +3269,9 @@
       <c r="Z20" s="1">
         <v>46033</v>
       </c>
+      <c r="AA20" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="AB20" s="2">
         <v>100</v>
       </c>
@@ -3277,6 +3331,9 @@
       <c r="Z21" s="1">
         <v>46034</v>
       </c>
+      <c r="AA21" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="AB21" s="2">
         <v>100</v>
       </c>
@@ -3336,6 +3393,9 @@
       <c r="Z22" s="1">
         <v>46035</v>
       </c>
+      <c r="AA22" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="AB22" s="2">
         <v>100</v>
       </c>
@@ -3395,6 +3455,9 @@
       <c r="Z23" s="1">
         <v>46036</v>
       </c>
+      <c r="AA23" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="AB23" s="2">
         <v>100</v>
       </c>
@@ -3454,6 +3517,9 @@
       <c r="Z24" s="1">
         <v>46037</v>
       </c>
+      <c r="AA24" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="AB24" s="2">
         <v>100</v>
       </c>
@@ -3513,6 +3579,9 @@
       <c r="Z25" s="1">
         <v>46038</v>
       </c>
+      <c r="AA25" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="AB25" s="2">
         <v>100</v>
       </c>
@@ -3572,6 +3641,9 @@
       <c r="Z26" s="1">
         <v>46039</v>
       </c>
+      <c r="AA26" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="AB26" s="2">
         <v>100</v>
       </c>
@@ -3631,6 +3703,9 @@
       <c r="Z27" s="1">
         <v>46040</v>
       </c>
+      <c r="AA27" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="AB27" s="2">
         <v>100</v>
       </c>
@@ -3684,6 +3759,9 @@
       <c r="Z28" s="1">
         <v>46041</v>
       </c>
+      <c r="AA28" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="AB28" s="2">
         <v>100</v>
       </c>
@@ -3737,6 +3815,9 @@
       <c r="Z29" s="1">
         <v>46042</v>
       </c>
+      <c r="AA29" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="AB29" s="2">
         <v>100</v>
       </c>
@@ -3790,6 +3871,9 @@
       <c r="Z30" s="1">
         <v>46043</v>
       </c>
+      <c r="AA30" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="AB30" s="2">
         <v>100</v>
       </c>
@@ -3834,6 +3918,9 @@
       <c r="Z31" s="1">
         <v>46044</v>
       </c>
+      <c r="AA31" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="AB31" s="2">
         <v>100</v>
       </c>
@@ -3878,11 +3965,14 @@
       <c r="Z32" s="1">
         <v>46045</v>
       </c>
+      <c r="AA32" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="AB32" s="2">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="14:24" ht="24" customHeight="1">
+    <row r="33" spans="14:28" ht="24" customHeight="1">
       <c r="N33" s="1">
         <v>45944</v>
       </c>
@@ -3910,8 +4000,17 @@
       <c r="X33" s="2">
         <v>500</v>
       </c>
-    </row>
-    <row r="34" spans="14:24" ht="24" customHeight="1">
+      <c r="Z33" s="1">
+        <v>46046</v>
+      </c>
+      <c r="AA33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB33" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="14:28" ht="24" customHeight="1">
       <c r="N34" s="1">
         <v>45945</v>
       </c>
@@ -3940,7 +4039,7 @@
         <v>12750</v>
       </c>
     </row>
-    <row r="35" spans="14:24" ht="24" customHeight="1">
+    <row r="35" spans="14:28" ht="24" customHeight="1">
       <c r="N35" s="1">
         <v>45946</v>
       </c>
@@ -3951,7 +4050,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="14:24" ht="24" customHeight="1">
+    <row r="36" spans="14:28" ht="24" customHeight="1">
       <c r="N36" s="1">
         <v>45947</v>
       </c>
@@ -3962,7 +4061,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="14:24" ht="24" customHeight="1">
+    <row r="37" spans="14:28" ht="24" customHeight="1">
       <c r="N37" s="1">
         <v>45948</v>
       </c>
@@ -3973,7 +4072,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="14:24" ht="24" customHeight="1">
+    <row r="38" spans="14:28" ht="24" customHeight="1">
       <c r="N38" s="1">
         <v>45949</v>
       </c>
@@ -3984,7 +4083,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="39" spans="14:24" ht="24" customHeight="1">
+    <row r="39" spans="14:28" ht="24" customHeight="1">
       <c r="N39" s="1">
         <v>45950</v>
       </c>
@@ -3995,7 +4094,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="40" spans="14:24" ht="24" customHeight="1">
+    <row r="40" spans="14:28" ht="24" customHeight="1">
       <c r="N40" s="1">
         <v>45951</v>
       </c>
@@ -4006,7 +4105,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="14:24" ht="24" customHeight="1">
+    <row r="41" spans="14:28" ht="24" customHeight="1">
       <c r="N41" s="1">
         <v>45952</v>
       </c>
@@ -4017,7 +4116,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="14:24" ht="24" customHeight="1">
+    <row r="42" spans="14:28" ht="24" customHeight="1">
       <c r="N42" s="1">
         <v>45953</v>
       </c>
@@ -4028,7 +4127,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="14:24" ht="24" customHeight="1">
+    <row r="43" spans="14:28" ht="24" customHeight="1">
       <c r="N43" s="1">
         <v>45954</v>
       </c>
@@ -4039,7 +4138,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="44" spans="14:24" ht="24" customHeight="1">
+    <row r="44" spans="14:28" ht="24" customHeight="1">
       <c r="N44" s="1">
         <v>45955</v>
       </c>
@@ -4052,6 +4151,14 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="Z2:Z4"/>
+    <mergeCell ref="AA2:AB3"/>
+    <mergeCell ref="V2:V4"/>
+    <mergeCell ref="W2:X3"/>
+    <mergeCell ref="N11:N13"/>
+    <mergeCell ref="O11:P12"/>
+    <mergeCell ref="N2:N4"/>
+    <mergeCell ref="O2:P3"/>
     <mergeCell ref="K2:L3"/>
     <mergeCell ref="R2:R4"/>
     <mergeCell ref="S2:T3"/>
@@ -4060,14 +4167,6 @@
     <mergeCell ref="F2:F4"/>
     <mergeCell ref="G2:H3"/>
     <mergeCell ref="J2:J4"/>
-    <mergeCell ref="Z2:Z4"/>
-    <mergeCell ref="AA2:AB3"/>
-    <mergeCell ref="V2:V4"/>
-    <mergeCell ref="W2:X3"/>
-    <mergeCell ref="N11:N13"/>
-    <mergeCell ref="O11:P12"/>
-    <mergeCell ref="N2:N4"/>
-    <mergeCell ref="O2:P3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4083,40 +4182,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="24" customHeight="1">
-      <c r="B2" s="47">
+      <c r="B2" s="48">
         <v>11</v>
       </c>
-      <c r="C2" s="41">
+      <c r="C2" s="42">
         <f>SUM(D5:D31)</f>
         <v>2750</v>
       </c>
-      <c r="D2" s="41"/>
-      <c r="F2" s="47">
-        <v>12</v>
-      </c>
-      <c r="G2" s="41">
+      <c r="D2" s="42"/>
+      <c r="F2" s="48">
+        <v>12</v>
+      </c>
+      <c r="G2" s="42">
         <f>SUM(H5:H29)</f>
         <v>15470</v>
       </c>
-      <c r="H2" s="41"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="2:8" ht="24" customHeight="1">
-      <c r="B3" s="47"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
     </row>
     <row r="4" spans="2:8" ht="24" customHeight="1">
-      <c r="B4" s="47"/>
+      <c r="B4" s="48"/>
       <c r="C4" s="21" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="47"/>
+      <c r="F4" s="48"/>
       <c r="G4" s="21" t="s">
         <v>0</v>
       </c>
@@ -4488,40 +4587,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="24" customHeight="1">
-      <c r="B2" s="47">
-        <v>12</v>
-      </c>
-      <c r="C2" s="41">
+      <c r="B2" s="48">
+        <v>12</v>
+      </c>
+      <c r="C2" s="42">
         <f>SUM(D6:D39)</f>
         <v>8500</v>
       </c>
-      <c r="D2" s="41"/>
-      <c r="F2" s="47">
+      <c r="D2" s="42"/>
+      <c r="F2" s="48">
         <v>1</v>
       </c>
-      <c r="G2" s="41">
+      <c r="G2" s="42">
         <f>SUM(H5:H39)</f>
         <v>1900</v>
       </c>
-      <c r="H2" s="41"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="2:8" ht="24" customHeight="1">
-      <c r="B3" s="47"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
     </row>
     <row r="4" spans="2:8" ht="24" customHeight="1">
-      <c r="B4" s="47"/>
+      <c r="B4" s="48"/>
       <c r="C4" s="24" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="47"/>
+      <c r="F4" s="48"/>
       <c r="G4" s="24" t="s">
         <v>0</v>
       </c>
@@ -5105,49 +5204,49 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="24" customHeight="1">
-      <c r="B2" s="47"/>
-      <c r="C2" s="41">
+      <c r="B2" s="48"/>
+      <c r="C2" s="42">
         <f>SUM(D5:D44)</f>
         <v>10500</v>
       </c>
-      <c r="D2" s="41"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="41">
+      <c r="D2" s="42"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="42">
         <f>SUM(H5:H44)</f>
-        <v>360</v>
-      </c>
-      <c r="H2" s="41"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
+        <v>420</v>
+      </c>
+      <c r="H2" s="42"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="42"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1">
-      <c r="B3" s="47"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
     </row>
     <row r="4" spans="1:13" ht="24" customHeight="1">
-      <c r="B4" s="47"/>
+      <c r="B4" s="48"/>
       <c r="C4" s="28" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="47"/>
+      <c r="F4" s="48"/>
       <c r="G4" s="33" t="s">
         <v>0</v>
       </c>
       <c r="H4" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="47"/>
+      <c r="K4" s="48"/>
       <c r="L4" s="28"/>
       <c r="M4" s="28"/>
     </row>
@@ -5350,7 +5449,15 @@
       <c r="D14" s="32">
         <v>60</v>
       </c>
-      <c r="F14" s="4"/>
+      <c r="F14" s="31">
+        <v>45681</v>
+      </c>
+      <c r="G14" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="29">
+        <v>60</v>
+      </c>
     </row>
     <row r="15" spans="1:13" ht="24" customHeight="1">
       <c r="A15" s="30"/>
@@ -5437,9 +5544,9 @@
       <c r="D21" s="32">
         <v>60</v>
       </c>
-      <c r="G21" s="48"/>
-      <c r="H21" s="48"/>
-      <c r="I21" s="48"/>
+      <c r="G21" s="49"/>
+      <c r="H21" s="49"/>
+      <c r="I21" s="49"/>
     </row>
     <row r="22" spans="1:9" ht="21">
       <c r="A22" s="30"/>
@@ -5452,9 +5559,9 @@
       <c r="D22" s="32">
         <v>60</v>
       </c>
-      <c r="G22" s="48"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="48"/>
+      <c r="G22" s="49"/>
+      <c r="H22" s="49"/>
+      <c r="I22" s="49"/>
     </row>
     <row r="23" spans="1:9" ht="21">
       <c r="A23" s="30"/>

--- a/BEDEL(2).xlsx
+++ b/BEDEL(2).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760" activeTab="6"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="MED LEMIN (2)" sheetId="4" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="32">
   <si>
     <t>Description</t>
   </si>
@@ -116,12 +116,18 @@
   <si>
     <t>CONX</t>
   </si>
+  <si>
+    <t>cnx</t>
+  </si>
+  <si>
+    <t>dimas</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -209,6 +215,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -245,7 +258,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -353,6 +366,150 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -700,40 +857,40 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="17.5703125" defaultRowHeight="24" customHeight="1"/>
   <sheetData>
     <row r="2" spans="2:8" ht="24" customHeight="1">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="89" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="42">
+      <c r="C2" s="90">
         <f>SUM(D5:D14)</f>
         <v>700</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="F2" s="43">
+      <c r="D2" s="90"/>
+      <c r="F2" s="91">
         <v>9</v>
       </c>
-      <c r="G2" s="42">
+      <c r="G2" s="90">
         <f>SUM(H5:H35)</f>
         <v>2175</v>
       </c>
-      <c r="H2" s="42"/>
+      <c r="H2" s="90"/>
     </row>
     <row r="3" spans="2:8" ht="24" customHeight="1">
-      <c r="B3" s="41"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
     </row>
     <row r="4" spans="2:8" ht="24" customHeight="1">
-      <c r="B4" s="41"/>
+      <c r="B4" s="89"/>
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="43"/>
+      <c r="F4" s="91"/>
       <c r="G4" s="8" t="s">
         <v>0</v>
       </c>
@@ -1176,20 +1333,20 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="17.5703125" defaultRowHeight="24" customHeight="1"/>
   <sheetData>
     <row r="2" spans="1:4" ht="24" customHeight="1">
-      <c r="B2" s="43"/>
-      <c r="C2" s="42">
+      <c r="B2" s="91"/>
+      <c r="C2" s="90">
         <f>SUM(D5:D31)</f>
         <v>2400</v>
       </c>
-      <c r="D2" s="42"/>
+      <c r="D2" s="90"/>
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
-      <c r="B3" s="43"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
     </row>
     <row r="4" spans="1:4" ht="24" customHeight="1">
-      <c r="B4" s="43"/>
+      <c r="B4" s="91"/>
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
@@ -1401,58 +1558,58 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="24" customHeight="1">
-      <c r="B2" s="44">
+      <c r="B2" s="92">
         <v>7</v>
       </c>
-      <c r="C2" s="45">
+      <c r="C2" s="93">
         <f>SUM(D5:D7)</f>
         <v>8500</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="F2" s="44">
+      <c r="D2" s="93"/>
+      <c r="F2" s="92">
         <v>8</v>
       </c>
-      <c r="G2" s="45">
+      <c r="G2" s="93">
         <f>SUM(H5:H7)</f>
         <v>8500</v>
       </c>
-      <c r="H2" s="45"/>
-      <c r="J2" s="44">
+      <c r="H2" s="93"/>
+      <c r="J2" s="92">
         <v>9</v>
       </c>
-      <c r="K2" s="45">
+      <c r="K2" s="93">
         <f>SUM(L5:L7)</f>
         <v>1500</v>
       </c>
-      <c r="L2" s="45"/>
+      <c r="L2" s="93"/>
     </row>
     <row r="3" spans="2:12" ht="24" customHeight="1">
-      <c r="B3" s="44"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+      <c r="J3" s="92"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
     </row>
     <row r="4" spans="2:12" ht="24" customHeight="1">
-      <c r="B4" s="44"/>
+      <c r="B4" s="92"/>
       <c r="C4" s="9" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="44"/>
+      <c r="F4" s="92"/>
       <c r="G4" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="J4" s="44"/>
+      <c r="J4" s="92"/>
       <c r="K4" s="9" t="s">
         <v>0</v>
       </c>
@@ -1523,56 +1680,56 @@
       <c r="F9" s="10"/>
     </row>
     <row r="10" spans="2:12" ht="24" customHeight="1">
-      <c r="B10" s="44">
+      <c r="B10" s="92">
         <v>10</v>
       </c>
-      <c r="C10" s="45">
+      <c r="C10" s="93">
         <f>SUM(D13:D39)</f>
         <v>8500</v>
       </c>
-      <c r="D10" s="45"/>
-      <c r="F10" s="44">
+      <c r="D10" s="93"/>
+      <c r="F10" s="92">
         <v>11</v>
       </c>
-      <c r="G10" s="45">
+      <c r="G10" s="93">
         <f>SUM(H13:H45)</f>
         <v>8500</v>
       </c>
-      <c r="H10" s="45"/>
-      <c r="J10" s="44"/>
-      <c r="K10" s="45">
+      <c r="H10" s="93"/>
+      <c r="J10" s="92"/>
+      <c r="K10" s="93">
         <f>SUM(L13:L44)</f>
         <v>4400</v>
       </c>
-      <c r="L10" s="45"/>
+      <c r="L10" s="93"/>
     </row>
     <row r="11" spans="2:12" ht="24" customHeight="1">
-      <c r="B11" s="44"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="J11" s="44"/>
-      <c r="K11" s="45"/>
-      <c r="L11" s="45"/>
+      <c r="B11" s="92"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
+      <c r="F11" s="92"/>
+      <c r="G11" s="93"/>
+      <c r="H11" s="93"/>
+      <c r="J11" s="92"/>
+      <c r="K11" s="93"/>
+      <c r="L11" s="93"/>
     </row>
     <row r="12" spans="2:12" ht="24" customHeight="1">
-      <c r="B12" s="44"/>
+      <c r="B12" s="92"/>
       <c r="C12" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D12" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F12" s="44"/>
+      <c r="F12" s="92"/>
       <c r="G12" s="16" t="s">
         <v>0</v>
       </c>
       <c r="H12" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="J12" s="44"/>
+      <c r="J12" s="92"/>
       <c r="K12" s="19" t="s">
         <v>0</v>
       </c>
@@ -2176,145 +2333,163 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:AB44"/>
+  <dimension ref="B2:AF61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="17.5703125" defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="16384" width="17.5703125" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:28" ht="24" customHeight="1">
-      <c r="B2" s="47">
+    <row r="2" spans="2:32" ht="24" customHeight="1">
+      <c r="B2" s="95">
         <v>6</v>
       </c>
-      <c r="C2" s="46">
+      <c r="C2" s="94">
         <f>SUM(D5:D31)</f>
         <v>13000</v>
       </c>
-      <c r="D2" s="46"/>
-      <c r="F2" s="47">
+      <c r="D2" s="94"/>
+      <c r="F2" s="95">
         <v>7</v>
       </c>
-      <c r="G2" s="46">
+      <c r="G2" s="94">
         <f>SUM(H5:H32)</f>
         <v>13000</v>
       </c>
-      <c r="H2" s="46"/>
-      <c r="J2" s="47">
+      <c r="H2" s="94"/>
+      <c r="J2" s="95">
         <v>8</v>
       </c>
-      <c r="K2" s="46">
+      <c r="K2" s="94">
         <f>SUM(L5:L32)</f>
         <v>13000</v>
       </c>
-      <c r="L2" s="46"/>
-      <c r="N2" s="47">
+      <c r="L2" s="94"/>
+      <c r="N2" s="95">
         <v>9</v>
       </c>
-      <c r="O2" s="46">
+      <c r="O2" s="94">
         <f>SUM(P5:P8)</f>
         <v>13000</v>
       </c>
-      <c r="P2" s="46"/>
-      <c r="R2" s="47">
+      <c r="P2" s="94"/>
+      <c r="R2" s="95">
         <v>11</v>
       </c>
-      <c r="S2" s="46">
+      <c r="S2" s="94">
         <f>SUM(T5:T35)</f>
         <v>13000</v>
       </c>
-      <c r="T2" s="46"/>
-      <c r="V2" s="47">
-        <v>12</v>
-      </c>
-      <c r="W2" s="46">
+      <c r="T2" s="94"/>
+      <c r="V2" s="95">
+        <v>12</v>
+      </c>
+      <c r="W2" s="94">
         <f>SUM(X5:X35)</f>
         <v>16500</v>
       </c>
-      <c r="X2" s="46"/>
-      <c r="Z2" s="47">
+      <c r="X2" s="94"/>
+      <c r="Z2" s="95">
         <v>1</v>
       </c>
-      <c r="AA2" s="46">
+      <c r="AA2" s="94">
         <f>SUM(AB5:AB35)</f>
-        <v>3100</v>
-      </c>
-      <c r="AB2" s="46"/>
-    </row>
-    <row r="3" spans="2:28" ht="24" customHeight="1">
-      <c r="B3" s="47"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="46"/>
-      <c r="P3" s="46"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="46"/>
-      <c r="T3" s="46"/>
-      <c r="V3" s="47"/>
-      <c r="W3" s="46"/>
-      <c r="X3" s="46"/>
-      <c r="Z3" s="47"/>
-      <c r="AA3" s="46"/>
-      <c r="AB3" s="46"/>
-    </row>
-    <row r="4" spans="2:28" ht="24" customHeight="1">
-      <c r="B4" s="47"/>
+        <v>16500</v>
+      </c>
+      <c r="AB2" s="94"/>
+      <c r="AD2" s="95">
+        <v>2</v>
+      </c>
+      <c r="AE2" s="94">
+        <f>SUM(AF6:AF37)</f>
+        <v>16500</v>
+      </c>
+      <c r="AF2" s="94"/>
+    </row>
+    <row r="3" spans="2:32" ht="24" customHeight="1">
+      <c r="B3" s="95"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="94"/>
+      <c r="J3" s="95"/>
+      <c r="K3" s="94"/>
+      <c r="L3" s="94"/>
+      <c r="N3" s="95"/>
+      <c r="O3" s="94"/>
+      <c r="P3" s="94"/>
+      <c r="R3" s="95"/>
+      <c r="S3" s="94"/>
+      <c r="T3" s="94"/>
+      <c r="V3" s="95"/>
+      <c r="W3" s="94"/>
+      <c r="X3" s="94"/>
+      <c r="Z3" s="95"/>
+      <c r="AA3" s="94"/>
+      <c r="AB3" s="94"/>
+      <c r="AD3" s="95"/>
+      <c r="AE3" s="94"/>
+      <c r="AF3" s="94"/>
+    </row>
+    <row r="4" spans="2:32" ht="24" customHeight="1">
+      <c r="B4" s="95"/>
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="47"/>
+      <c r="F4" s="95"/>
       <c r="G4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="J4" s="47"/>
+      <c r="J4" s="95"/>
       <c r="K4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="N4" s="47"/>
+      <c r="N4" s="95"/>
       <c r="O4" s="6" t="s">
         <v>0</v>
       </c>
       <c r="P4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="R4" s="47"/>
+      <c r="R4" s="95"/>
       <c r="S4" s="18" t="s">
         <v>0</v>
       </c>
       <c r="T4" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="V4" s="47"/>
+      <c r="V4" s="95"/>
       <c r="W4" s="20" t="s">
         <v>0</v>
       </c>
       <c r="X4" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="Z4" s="47"/>
+      <c r="Z4" s="95"/>
       <c r="AA4" s="23" t="s">
         <v>0</v>
       </c>
       <c r="AB4" s="23" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="2:28" ht="24" customHeight="1">
+      <c r="AD4" s="95"/>
+      <c r="AE4" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="41" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:32" ht="24" customHeight="1">
       <c r="B5" s="1">
         <v>45806</v>
       </c>
@@ -2372,8 +2547,17 @@
       <c r="AB5" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="6" spans="2:28" ht="24" customHeight="1">
+      <c r="AD5" s="1">
+        <v>46047</v>
+      </c>
+      <c r="AE5" s="65" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF5" s="65" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="2:32" ht="24" customHeight="1">
       <c r="B6" s="1">
         <v>45807</v>
       </c>
@@ -2434,8 +2618,17 @@
       <c r="AB6" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="7" spans="2:28" ht="24" customHeight="1">
+      <c r="AD6" s="1">
+        <v>46048</v>
+      </c>
+      <c r="AE6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF6" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="2:32" ht="24" customHeight="1">
       <c r="B7" s="1">
         <v>45809</v>
       </c>
@@ -2496,8 +2689,17 @@
       <c r="AB7" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="8" spans="2:28" ht="24" customHeight="1">
+      <c r="AD7" s="1">
+        <v>46049</v>
+      </c>
+      <c r="AE7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF7" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="2:32" ht="24" customHeight="1">
       <c r="B8" s="1">
         <v>45810</v>
       </c>
@@ -2558,8 +2760,17 @@
       <c r="AB8" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="9" spans="2:28" ht="24" customHeight="1">
+      <c r="AD8" s="1">
+        <v>46050</v>
+      </c>
+      <c r="AE8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF8" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="2:32" ht="24" customHeight="1">
       <c r="B9" s="1">
         <v>45811</v>
       </c>
@@ -2611,8 +2822,17 @@
       <c r="AB9" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="2:28" ht="24" customHeight="1">
+      <c r="AD9" s="1">
+        <v>46051</v>
+      </c>
+      <c r="AE9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF9" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="2:32" ht="24" customHeight="1">
       <c r="B10" s="1">
         <v>45812</v>
       </c>
@@ -2664,8 +2884,17 @@
       <c r="AB10" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="11" spans="2:28" ht="24" customHeight="1">
+      <c r="AD10" s="1">
+        <v>46052</v>
+      </c>
+      <c r="AE10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF10" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="2:32" ht="24" customHeight="1">
       <c r="B11" s="1">
         <v>45813</v>
       </c>
@@ -2690,14 +2919,14 @@
       <c r="L11" s="2">
         <v>100</v>
       </c>
-      <c r="N11" s="47">
+      <c r="N11" s="95">
         <v>10</v>
       </c>
-      <c r="O11" s="46">
+      <c r="O11" s="94">
         <f>SUM(P14:P44)</f>
         <v>13000</v>
       </c>
-      <c r="P11" s="46"/>
+      <c r="P11" s="94"/>
       <c r="R11" s="1">
         <v>45962</v>
       </c>
@@ -2725,8 +2954,17 @@
       <c r="AB11" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="12" spans="2:28" ht="24" customHeight="1">
+      <c r="AD11" s="1">
+        <v>46053</v>
+      </c>
+      <c r="AE11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF11" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="2:32" ht="24" customHeight="1">
       <c r="B12" s="1">
         <v>45815</v>
       </c>
@@ -2751,9 +2989,9 @@
       <c r="L12" s="2">
         <v>100</v>
       </c>
-      <c r="N12" s="47"/>
-      <c r="O12" s="46"/>
-      <c r="P12" s="46"/>
+      <c r="N12" s="95"/>
+      <c r="O12" s="94"/>
+      <c r="P12" s="94"/>
       <c r="R12" s="1">
         <v>45963</v>
       </c>
@@ -2781,8 +3019,17 @@
       <c r="AB12" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="2:28" ht="24" customHeight="1">
+      <c r="AD12" s="1">
+        <v>46054</v>
+      </c>
+      <c r="AE12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF12" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="2:32" ht="24" customHeight="1">
       <c r="B13" s="1">
         <v>45817</v>
       </c>
@@ -2807,7 +3054,7 @@
       <c r="L13" s="2">
         <v>100</v>
       </c>
-      <c r="N13" s="47"/>
+      <c r="N13" s="95"/>
       <c r="O13" s="14" t="s">
         <v>0</v>
       </c>
@@ -2841,8 +3088,17 @@
       <c r="AB13" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="14" spans="2:28" ht="24" customHeight="1">
+      <c r="AD13" s="1">
+        <v>46055</v>
+      </c>
+      <c r="AE13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF13" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="2:32" ht="24" customHeight="1">
       <c r="B14" s="1">
         <v>45818</v>
       </c>
@@ -2903,8 +3159,17 @@
       <c r="AB14" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="15" spans="2:28" ht="24" customHeight="1">
+      <c r="AD14" s="1">
+        <v>46056</v>
+      </c>
+      <c r="AE14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF14" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="2:32" ht="24" customHeight="1">
       <c r="B15" s="1">
         <v>45819</v>
       </c>
@@ -2965,8 +3230,17 @@
       <c r="AB15" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="16" spans="2:28" ht="24" customHeight="1">
+      <c r="AD15" s="1">
+        <v>46057</v>
+      </c>
+      <c r="AE15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF15" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="2:32" ht="24" customHeight="1">
       <c r="B16" s="1">
         <v>45820</v>
       </c>
@@ -3027,8 +3301,17 @@
       <c r="AB16" s="2">
         <v>200</v>
       </c>
-    </row>
-    <row r="17" spans="2:28" ht="24" customHeight="1">
+      <c r="AD16" s="1">
+        <v>46058</v>
+      </c>
+      <c r="AE16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF16" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="2:32" ht="24" customHeight="1">
       <c r="B17" s="1">
         <v>45821</v>
       </c>
@@ -3089,8 +3372,17 @@
       <c r="AB17" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="2:28" ht="24" customHeight="1">
+      <c r="AD17" s="1">
+        <v>46059</v>
+      </c>
+      <c r="AE17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF17" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="2:32" ht="24" customHeight="1">
       <c r="B18" s="1">
         <v>45821</v>
       </c>
@@ -3151,8 +3443,17 @@
       <c r="AB18" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="19" spans="2:28" ht="24" customHeight="1">
+      <c r="AD18" s="1">
+        <v>46060</v>
+      </c>
+      <c r="AE18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF18" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="2:32" ht="24" customHeight="1">
       <c r="B19" s="1">
         <v>45822</v>
       </c>
@@ -3213,8 +3514,17 @@
       <c r="AB19" s="2">
         <v>200</v>
       </c>
-    </row>
-    <row r="20" spans="2:28" ht="24" customHeight="1">
+      <c r="AD19" s="1">
+        <v>46061</v>
+      </c>
+      <c r="AE19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF19" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="2:32" ht="24" customHeight="1">
       <c r="B20" s="1">
         <v>45823</v>
       </c>
@@ -3275,8 +3585,17 @@
       <c r="AB20" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="2:28" ht="24" customHeight="1">
+      <c r="AD20" s="1">
+        <v>46062</v>
+      </c>
+      <c r="AE20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF20" s="2">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="21" spans="2:32" ht="24" customHeight="1">
       <c r="B21" s="1">
         <v>45823</v>
       </c>
@@ -3337,8 +3656,17 @@
       <c r="AB21" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="22" spans="2:28" ht="24" customHeight="1">
+      <c r="AD21" s="1">
+        <v>46063</v>
+      </c>
+      <c r="AE21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF21" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="2:32" ht="24" customHeight="1">
       <c r="B22" s="1">
         <v>45825</v>
       </c>
@@ -3399,8 +3727,17 @@
       <c r="AB22" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="2:28" ht="24" customHeight="1">
+      <c r="AD22" s="1">
+        <v>46064</v>
+      </c>
+      <c r="AE22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF22" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="2:32" ht="24" customHeight="1">
       <c r="B23" s="1">
         <v>45826</v>
       </c>
@@ -3461,8 +3798,17 @@
       <c r="AB23" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="24" spans="2:28" ht="24" customHeight="1">
+      <c r="AD23" s="1">
+        <v>46065</v>
+      </c>
+      <c r="AE23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF23" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="2:32" ht="24" customHeight="1">
       <c r="B24" s="1">
         <v>45827</v>
       </c>
@@ -3523,8 +3869,17 @@
       <c r="AB24" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="2:28" ht="24" customHeight="1">
+      <c r="AD24" s="1">
+        <v>46066</v>
+      </c>
+      <c r="AE24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF24" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="2:32" ht="24" customHeight="1">
       <c r="B25" s="1">
         <v>45828</v>
       </c>
@@ -3585,8 +3940,17 @@
       <c r="AB25" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="26" spans="2:28" ht="24" customHeight="1">
+      <c r="AD25" s="1">
+        <v>46067</v>
+      </c>
+      <c r="AE25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF25" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="2:32" ht="24" customHeight="1">
       <c r="B26" s="1">
         <v>45829</v>
       </c>
@@ -3647,8 +4011,17 @@
       <c r="AB26" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="27" spans="2:28" ht="24" customHeight="1">
+      <c r="AD26" s="1">
+        <v>46068</v>
+      </c>
+      <c r="AE26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF26" s="2">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="27" spans="2:32" ht="24" customHeight="1">
       <c r="B27" s="1">
         <v>45830</v>
       </c>
@@ -3709,8 +4082,17 @@
       <c r="AB27" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="28" spans="2:28" ht="24" customHeight="1">
+      <c r="AD27" s="1">
+        <v>46068</v>
+      </c>
+      <c r="AE27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF27" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="2:32" ht="24" customHeight="1">
       <c r="B28" s="1">
         <v>45831</v>
       </c>
@@ -3765,8 +4147,17 @@
       <c r="AB28" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="29" spans="2:28" ht="24" customHeight="1">
+      <c r="AD28" s="1">
+        <v>46069</v>
+      </c>
+      <c r="AE28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF28" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="2:32" ht="24" customHeight="1">
       <c r="B29" s="1">
         <v>45832</v>
       </c>
@@ -3821,8 +4212,17 @@
       <c r="AB29" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="30" spans="2:28" ht="24" customHeight="1">
+      <c r="AD29" s="1">
+        <v>46070</v>
+      </c>
+      <c r="AE29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF29" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="2:32" ht="24" customHeight="1">
       <c r="B30" s="1">
         <v>45834</v>
       </c>
@@ -3877,8 +4277,17 @@
       <c r="AB30" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="31" spans="2:28" ht="24" customHeight="1">
+      <c r="AD30" s="1">
+        <v>46071</v>
+      </c>
+      <c r="AE30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF30" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="2:32" ht="24" customHeight="1">
       <c r="F31" s="1">
         <v>45863</v>
       </c>
@@ -3924,8 +4333,17 @@
       <c r="AB31" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="32" spans="2:28" ht="24" customHeight="1">
+      <c r="AD31" s="1">
+        <v>46072</v>
+      </c>
+      <c r="AE31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF31" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="2:32" ht="24" customHeight="1">
       <c r="F32" s="1">
         <v>45864</v>
       </c>
@@ -3971,8 +4389,17 @@
       <c r="AB32" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="33" spans="14:28" ht="24" customHeight="1">
+      <c r="AD32" s="1">
+        <v>46073</v>
+      </c>
+      <c r="AE32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF32" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" ht="24" customHeight="1">
       <c r="N33" s="1">
         <v>45944</v>
       </c>
@@ -4009,8 +4436,17 @@
       <c r="AB33" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="34" spans="14:28" ht="24" customHeight="1">
+      <c r="AD33" s="1">
+        <v>46074</v>
+      </c>
+      <c r="AE33" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF33" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" ht="24" customHeight="1">
       <c r="N34" s="1">
         <v>45945</v>
       </c>
@@ -4038,8 +4474,40 @@
       <c r="X34" s="2">
         <v>12750</v>
       </c>
-    </row>
-    <row r="35" spans="14:28" ht="24" customHeight="1">
+      <c r="Z34" s="1">
+        <v>46047</v>
+      </c>
+      <c r="AA34" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB34" s="2">
+        <v>13400</v>
+      </c>
+      <c r="AD34" s="1">
+        <v>46075</v>
+      </c>
+      <c r="AE34" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF34" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" ht="24" customHeight="1">
+      <c r="B35" s="95"/>
+      <c r="C35" s="94">
+        <f>SUM(D38:D70)</f>
+        <v>2750</v>
+      </c>
+      <c r="D35" s="94"/>
+      <c r="F35" s="95">
+        <v>3</v>
+      </c>
+      <c r="G35" s="94">
+        <f>SUM(H38:H73)</f>
+        <v>8600</v>
+      </c>
+      <c r="H35" s="94"/>
       <c r="N35" s="1">
         <v>45946</v>
       </c>
@@ -4049,8 +4517,23 @@
       <c r="P35" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="36" spans="14:28" ht="24" customHeight="1">
+      <c r="AD35" s="1">
+        <v>46076</v>
+      </c>
+      <c r="AE35" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF35" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="2:32" ht="24" customHeight="1">
+      <c r="B36" s="95"/>
+      <c r="C36" s="94"/>
+      <c r="D36" s="94"/>
+      <c r="F36" s="95"/>
+      <c r="G36" s="94"/>
+      <c r="H36" s="94"/>
       <c r="N36" s="1">
         <v>45947</v>
       </c>
@@ -4060,8 +4543,31 @@
       <c r="P36" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="37" spans="14:28" ht="24" customHeight="1">
+      <c r="AD36" s="1">
+        <v>46077</v>
+      </c>
+      <c r="AE36" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF36" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" ht="24" customHeight="1">
+      <c r="B37" s="95"/>
+      <c r="C37" s="66" t="s">
+        <v>0</v>
+      </c>
+      <c r="D37" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="95"/>
+      <c r="G37" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="H37" s="73" t="s">
+        <v>1</v>
+      </c>
       <c r="N37" s="1">
         <v>45948</v>
       </c>
@@ -4071,8 +4577,35 @@
       <c r="P37" s="2">
         <v>100</v>
       </c>
-    </row>
-    <row r="38" spans="14:28" ht="24" customHeight="1">
+      <c r="AD37" s="1">
+        <v>46077</v>
+      </c>
+      <c r="AE37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF37" s="2">
+        <v>9750</v>
+      </c>
+    </row>
+    <row r="38" spans="2:32" ht="24" customHeight="1">
+      <c r="B38" s="1">
+        <v>46078</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" s="2">
+        <v>100</v>
+      </c>
+      <c r="F38" s="1">
+        <v>46083</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="N38" s="1">
         <v>45949</v>
       </c>
@@ -4083,7 +4616,25 @@
         <v>100</v>
       </c>
     </row>
-    <row r="39" spans="14:28" ht="24" customHeight="1">
+    <row r="39" spans="2:32" ht="24" customHeight="1">
+      <c r="B39" s="1">
+        <v>46079</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F39" s="1">
+        <v>46084</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="N39" s="1">
         <v>45950</v>
       </c>
@@ -4094,7 +4645,25 @@
         <v>300</v>
       </c>
     </row>
-    <row r="40" spans="14:28" ht="24" customHeight="1">
+    <row r="40" spans="2:32" ht="24" customHeight="1">
+      <c r="B40" s="1">
+        <v>46080</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F40" s="1">
+        <v>46085</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H40" s="2">
+        <v>200</v>
+      </c>
       <c r="N40" s="1">
         <v>45951</v>
       </c>
@@ -4105,7 +4674,25 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="14:28" ht="24" customHeight="1">
+    <row r="41" spans="2:32" ht="24" customHeight="1">
+      <c r="B41" s="1">
+        <v>46081</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F41" s="1">
+        <v>46086</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" s="2">
+        <v>100</v>
+      </c>
       <c r="N41" s="1">
         <v>45952</v>
       </c>
@@ -4116,7 +4703,25 @@
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="14:28" ht="24" customHeight="1">
+    <row r="42" spans="2:32" ht="24" customHeight="1">
+      <c r="B42" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F42" s="1">
+        <v>46087</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="N42" s="1">
         <v>45953</v>
       </c>
@@ -4127,7 +4732,22 @@
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="14:28" ht="24" customHeight="1">
+    <row r="43" spans="2:32" ht="24" customHeight="1">
+      <c r="B43" s="1">
+        <v>46084</v>
+      </c>
+      <c r="D43" s="2">
+        <v>2650</v>
+      </c>
+      <c r="F43" s="1">
+        <v>46088</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" s="2">
+        <v>100</v>
+      </c>
       <c r="N43" s="1">
         <v>45954</v>
       </c>
@@ -4138,7 +4758,16 @@
         <v>100</v>
       </c>
     </row>
-    <row r="44" spans="14:28" ht="24" customHeight="1">
+    <row r="44" spans="2:32" ht="24" customHeight="1">
+      <c r="F44" s="1">
+        <v>46089</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H44" s="2">
+        <v>100</v>
+      </c>
       <c r="N44" s="1">
         <v>45955</v>
       </c>
@@ -4149,24 +4778,217 @@
         <v>9800</v>
       </c>
     </row>
+    <row r="45" spans="2:32" ht="24" customHeight="1">
+      <c r="F45" s="1">
+        <v>46090</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" ht="24" customHeight="1">
+      <c r="F46" s="1">
+        <v>46091</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" ht="24" customHeight="1">
+      <c r="F47" s="1">
+        <v>46092</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" ht="24" customHeight="1">
+      <c r="F48" s="1">
+        <v>46093</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H48" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="49" spans="6:8" ht="24" customHeight="1">
+      <c r="F49" s="1">
+        <v>46094</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="50" spans="6:8" ht="24" customHeight="1">
+      <c r="F50" s="1">
+        <v>46095</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="51" spans="6:8" ht="24" customHeight="1">
+      <c r="F51" s="1">
+        <v>46096</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="52" spans="6:8" ht="24" customHeight="1">
+      <c r="F52" s="1">
+        <v>46097</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H52" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="6:8" ht="24" customHeight="1">
+      <c r="F53" s="1">
+        <v>46098</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H53" s="2">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="54" spans="6:8" ht="24" customHeight="1">
+      <c r="F54" s="1">
+        <v>46099</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="55" spans="6:8" ht="24" customHeight="1">
+      <c r="F55" s="1">
+        <v>46100</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H55" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="6:8" ht="24" customHeight="1">
+      <c r="F56" s="1">
+        <v>46101</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57" spans="6:8" ht="24" customHeight="1">
+      <c r="F57" s="1">
+        <v>46102</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H57" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="58" spans="6:8" ht="24" customHeight="1">
+      <c r="F58" s="1">
+        <v>46103</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H58" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="6:8" ht="24" customHeight="1">
+      <c r="F59" s="1">
+        <v>46104</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="6:8" ht="24" customHeight="1">
+      <c r="F60" s="1">
+        <v>46105</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H60" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="6:8" ht="24" customHeight="1">
+      <c r="F61" s="1">
+        <v>46106</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H61" s="2">
+        <v>1200</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="22">
+    <mergeCell ref="AE2:AF3"/>
+    <mergeCell ref="K2:L3"/>
+    <mergeCell ref="R2:R4"/>
+    <mergeCell ref="S2:T3"/>
     <mergeCell ref="Z2:Z4"/>
     <mergeCell ref="AA2:AB3"/>
     <mergeCell ref="V2:V4"/>
     <mergeCell ref="W2:X3"/>
-    <mergeCell ref="N11:N13"/>
+    <mergeCell ref="AD2:AD4"/>
     <mergeCell ref="O11:P12"/>
     <mergeCell ref="N2:N4"/>
     <mergeCell ref="O2:P3"/>
-    <mergeCell ref="K2:L3"/>
-    <mergeCell ref="R2:R4"/>
-    <mergeCell ref="S2:T3"/>
     <mergeCell ref="C2:D3"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:D36"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="F2:F4"/>
     <mergeCell ref="G2:H3"/>
     <mergeCell ref="J2:J4"/>
+    <mergeCell ref="N11:N13"/>
+    <mergeCell ref="F35:F37"/>
+    <mergeCell ref="G35:H36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4182,40 +5004,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="24" customHeight="1">
-      <c r="B2" s="48">
+      <c r="B2" s="96">
         <v>11</v>
       </c>
-      <c r="C2" s="42">
+      <c r="C2" s="90">
         <f>SUM(D5:D31)</f>
         <v>2750</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="F2" s="48">
-        <v>12</v>
-      </c>
-      <c r="G2" s="42">
+      <c r="D2" s="90"/>
+      <c r="F2" s="96">
+        <v>12</v>
+      </c>
+      <c r="G2" s="90">
         <f>SUM(H5:H29)</f>
         <v>15470</v>
       </c>
-      <c r="H2" s="42"/>
+      <c r="H2" s="90"/>
     </row>
     <row r="3" spans="2:8" ht="24" customHeight="1">
-      <c r="B3" s="48"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
+      <c r="B3" s="96"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
     </row>
     <row r="4" spans="2:8" ht="24" customHeight="1">
-      <c r="B4" s="48"/>
+      <c r="B4" s="96"/>
       <c r="C4" s="21" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="48"/>
+      <c r="F4" s="96"/>
       <c r="G4" s="21" t="s">
         <v>0</v>
       </c>
@@ -4580,55 +5402,91 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:H38"/>
+  <dimension ref="B2:Q38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="17.5703125" defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="16384" width="17.5703125" style="25"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="24" customHeight="1">
-      <c r="B2" s="48">
-        <v>12</v>
-      </c>
-      <c r="C2" s="42">
+    <row r="2" spans="2:16" ht="24" customHeight="1">
+      <c r="B2" s="96">
+        <v>12</v>
+      </c>
+      <c r="C2" s="90">
         <f>SUM(D6:D39)</f>
         <v>8500</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="F2" s="48">
+      <c r="D2" s="90"/>
+      <c r="F2" s="96">
         <v>1</v>
       </c>
-      <c r="G2" s="42">
+      <c r="G2" s="90">
         <f>SUM(H5:H39)</f>
-        <v>1900</v>
-      </c>
-      <c r="H2" s="42"/>
-    </row>
-    <row r="3" spans="2:8" ht="24" customHeight="1">
-      <c r="B3" s="48"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-    </row>
-    <row r="4" spans="2:8" ht="24" customHeight="1">
-      <c r="B4" s="48"/>
+        <v>10500</v>
+      </c>
+      <c r="H2" s="90"/>
+      <c r="J2" s="96">
+        <v>2</v>
+      </c>
+      <c r="K2" s="90">
+        <f>SUM(L5:L39)</f>
+        <v>10150</v>
+      </c>
+      <c r="L2" s="90"/>
+      <c r="N2" s="96">
+        <v>3</v>
+      </c>
+      <c r="O2" s="90">
+        <f>SUM(P5:P39)</f>
+        <v>2000</v>
+      </c>
+      <c r="P2" s="90"/>
+    </row>
+    <row r="3" spans="2:16" ht="24" customHeight="1">
+      <c r="B3" s="96"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="90"/>
+      <c r="L3" s="90"/>
+      <c r="N3" s="96"/>
+      <c r="O3" s="90"/>
+      <c r="P3" s="90"/>
+    </row>
+    <row r="4" spans="2:16" ht="24" customHeight="1">
+      <c r="B4" s="96"/>
       <c r="C4" s="24" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="48"/>
+      <c r="F4" s="96"/>
       <c r="G4" s="24" t="s">
         <v>0</v>
       </c>
       <c r="H4" s="24" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="2:8" ht="24" customHeight="1">
+      <c r="J4" s="96"/>
+      <c r="K4" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="L4" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4" s="96"/>
+      <c r="O4" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="P4" s="71" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" ht="24" customHeight="1">
       <c r="B5" s="4">
         <v>45992</v>
       </c>
@@ -4645,8 +5503,26 @@
       <c r="H5" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="6" spans="2:8" ht="24" customHeight="1">
+      <c r="J5" s="4">
+        <v>46056</v>
+      </c>
+      <c r="K5" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="L5" s="46">
+        <v>100</v>
+      </c>
+      <c r="N5" s="4">
+        <v>46083</v>
+      </c>
+      <c r="O5" s="72" t="s">
+        <v>5</v>
+      </c>
+      <c r="P5" s="25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" ht="24" customHeight="1">
       <c r="B6" s="4">
         <v>45993</v>
       </c>
@@ -4662,8 +5538,27 @@
       <c r="H6" s="26">
         <v>100</v>
       </c>
-    </row>
-    <row r="7" spans="2:8" ht="24" customHeight="1">
+      <c r="J6" s="4">
+        <v>46057</v>
+      </c>
+      <c r="K6" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="L6" s="25">
+        <v>100</v>
+      </c>
+      <c r="M6" s="70"/>
+      <c r="N6" s="4">
+        <v>46084</v>
+      </c>
+      <c r="O6" s="72" t="s">
+        <v>5</v>
+      </c>
+      <c r="P6" s="25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" ht="24" customHeight="1">
       <c r="B7" s="4">
         <v>45994</v>
       </c>
@@ -4679,8 +5574,27 @@
       <c r="H7" s="26">
         <v>100</v>
       </c>
-    </row>
-    <row r="8" spans="2:8" ht="24" customHeight="1">
+      <c r="J7" s="4">
+        <v>46058</v>
+      </c>
+      <c r="K7" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="L7" s="48">
+        <v>100</v>
+      </c>
+      <c r="M7" s="70"/>
+      <c r="N7" s="4">
+        <v>46085</v>
+      </c>
+      <c r="O7" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="P7" s="25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" ht="24" customHeight="1">
       <c r="B8" s="4">
         <v>45995</v>
       </c>
@@ -4699,8 +5613,27 @@
       <c r="H8" s="26">
         <v>100</v>
       </c>
-    </row>
-    <row r="9" spans="2:8" ht="24" customHeight="1">
+      <c r="J8" s="4">
+        <v>46059</v>
+      </c>
+      <c r="K8" s="49" t="s">
+        <v>5</v>
+      </c>
+      <c r="L8" s="49">
+        <v>100</v>
+      </c>
+      <c r="M8" s="70"/>
+      <c r="N8" s="4">
+        <v>46086</v>
+      </c>
+      <c r="O8" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="P8" s="25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" ht="24" customHeight="1">
       <c r="B9" s="4">
         <v>45996</v>
       </c>
@@ -4719,8 +5652,27 @@
       <c r="H9" s="27">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="2:8" ht="24" customHeight="1">
+      <c r="J9" s="4">
+        <v>46060</v>
+      </c>
+      <c r="K9" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="L9" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="M9" s="70"/>
+      <c r="N9" s="4">
+        <v>46087</v>
+      </c>
+      <c r="O9" s="75" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" ht="24" customHeight="1">
       <c r="B10" s="4">
         <v>45997</v>
       </c>
@@ -4739,8 +5691,27 @@
       <c r="H10" s="27">
         <v>100</v>
       </c>
-    </row>
-    <row r="11" spans="2:8" ht="24" customHeight="1">
+      <c r="J10" s="4">
+        <v>46061</v>
+      </c>
+      <c r="K10" s="50" t="s">
+        <v>5</v>
+      </c>
+      <c r="L10" s="25">
+        <v>100</v>
+      </c>
+      <c r="M10" s="70"/>
+      <c r="N10" s="4">
+        <v>46088</v>
+      </c>
+      <c r="O10" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="P10" s="76" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" ht="24" customHeight="1">
       <c r="B11" s="4">
         <v>45998</v>
       </c>
@@ -4759,8 +5730,27 @@
       <c r="H11" s="27">
         <v>100</v>
       </c>
-    </row>
-    <row r="12" spans="2:8" ht="24" customHeight="1">
+      <c r="J11" s="4">
+        <v>46062</v>
+      </c>
+      <c r="K11" s="51" t="s">
+        <v>5</v>
+      </c>
+      <c r="L11" s="51">
+        <v>100</v>
+      </c>
+      <c r="M11" s="70"/>
+      <c r="N11" s="4">
+        <v>46089</v>
+      </c>
+      <c r="O11" s="76" t="s">
+        <v>5</v>
+      </c>
+      <c r="P11" s="25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" ht="24" customHeight="1">
       <c r="B12" s="4">
         <v>45999</v>
       </c>
@@ -4779,8 +5769,27 @@
       <c r="H12" s="27" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="2:8" ht="24" customHeight="1">
+      <c r="J12" s="4">
+        <v>46063</v>
+      </c>
+      <c r="K12" s="52" t="s">
+        <v>5</v>
+      </c>
+      <c r="L12" s="52">
+        <v>100</v>
+      </c>
+      <c r="M12" s="70"/>
+      <c r="N12" s="4">
+        <v>46090</v>
+      </c>
+      <c r="O12" s="77" t="s">
+        <v>5</v>
+      </c>
+      <c r="P12" s="77">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" ht="24" customHeight="1">
       <c r="B13" s="4">
         <v>46000</v>
       </c>
@@ -4799,8 +5808,27 @@
       <c r="H13" s="29">
         <v>100</v>
       </c>
-    </row>
-    <row r="14" spans="2:8" ht="24" customHeight="1">
+      <c r="J13" s="4">
+        <v>46064</v>
+      </c>
+      <c r="K13" s="53" t="s">
+        <v>5</v>
+      </c>
+      <c r="L13" s="53">
+        <v>100</v>
+      </c>
+      <c r="M13" s="70"/>
+      <c r="N13" s="4">
+        <v>46091</v>
+      </c>
+      <c r="O13" s="77" t="s">
+        <v>5</v>
+      </c>
+      <c r="P13" s="77">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" ht="24" customHeight="1">
       <c r="B14" s="4">
         <v>46001</v>
       </c>
@@ -4819,8 +5847,27 @@
       <c r="H14" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="15" spans="2:8" ht="24" customHeight="1">
+      <c r="J14" s="4">
+        <v>46065</v>
+      </c>
+      <c r="K14" s="53" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="53">
+        <v>100</v>
+      </c>
+      <c r="M14" s="70"/>
+      <c r="N14" s="4">
+        <v>46092</v>
+      </c>
+      <c r="O14" s="77" t="s">
+        <v>28</v>
+      </c>
+      <c r="P14" s="77" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" ht="24" customHeight="1">
       <c r="B15" s="4">
         <v>46002</v>
       </c>
@@ -4839,8 +5886,27 @@
       <c r="H15" s="30">
         <v>100</v>
       </c>
-    </row>
-    <row r="16" spans="2:8" ht="24" customHeight="1">
+      <c r="J15" s="4">
+        <v>46066</v>
+      </c>
+      <c r="K15" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="L15" s="54">
+        <v>100</v>
+      </c>
+      <c r="M15" s="70"/>
+      <c r="N15" s="4">
+        <v>46093</v>
+      </c>
+      <c r="O15" s="77" t="s">
+        <v>28</v>
+      </c>
+      <c r="P15" s="77" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" ht="24" customHeight="1">
       <c r="B16" s="4">
         <v>46003</v>
       </c>
@@ -4859,8 +5925,27 @@
       <c r="H16" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" ht="24" customHeight="1">
+      <c r="J16" s="4">
+        <v>46067</v>
+      </c>
+      <c r="K16" s="55" t="s">
+        <v>28</v>
+      </c>
+      <c r="L16" s="55" t="s">
+        <v>28</v>
+      </c>
+      <c r="M16" s="70"/>
+      <c r="N16" s="4">
+        <v>46094</v>
+      </c>
+      <c r="O16" s="77" t="s">
+        <v>28</v>
+      </c>
+      <c r="P16" s="77" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" ht="24" customHeight="1">
       <c r="B17" s="4">
         <v>46004</v>
       </c>
@@ -4879,8 +5964,27 @@
       <c r="H17" s="34">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" ht="24" customHeight="1">
+      <c r="J17" s="4">
+        <v>46068</v>
+      </c>
+      <c r="K17" s="56" t="s">
+        <v>5</v>
+      </c>
+      <c r="L17" s="25">
+        <v>100</v>
+      </c>
+      <c r="M17" s="70"/>
+      <c r="N17" s="4">
+        <v>46095</v>
+      </c>
+      <c r="O17" s="78" t="s">
+        <v>28</v>
+      </c>
+      <c r="P17" s="78" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" ht="24" customHeight="1">
       <c r="B18" s="4">
         <v>46005</v>
       </c>
@@ -4899,8 +6003,27 @@
       <c r="H18" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="19" spans="2:8" ht="24" customHeight="1">
+      <c r="J18" s="4">
+        <v>46069</v>
+      </c>
+      <c r="K18" s="58" t="s">
+        <v>5</v>
+      </c>
+      <c r="L18" s="25">
+        <v>100</v>
+      </c>
+      <c r="M18" s="70"/>
+      <c r="N18" s="4">
+        <v>46096</v>
+      </c>
+      <c r="O18" s="78" t="s">
+        <v>5</v>
+      </c>
+      <c r="P18" s="25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" ht="24" customHeight="1">
       <c r="B19" s="4">
         <v>46006</v>
       </c>
@@ -4919,8 +6042,27 @@
       <c r="H19" s="35" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="20" spans="2:8" ht="24" customHeight="1">
+      <c r="J19" s="4">
+        <v>46070</v>
+      </c>
+      <c r="K19" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="L19" s="25">
+        <v>100</v>
+      </c>
+      <c r="M19" s="70"/>
+      <c r="N19" s="4">
+        <v>46097</v>
+      </c>
+      <c r="O19" s="78" t="s">
+        <v>5</v>
+      </c>
+      <c r="P19" s="25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17" ht="24" customHeight="1">
       <c r="B20" s="4">
         <v>46007</v>
       </c>
@@ -4939,8 +6081,27 @@
       <c r="H20" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="2:8" ht="24" customHeight="1">
+      <c r="J20" s="4">
+        <v>46071</v>
+      </c>
+      <c r="K20" s="60" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="25">
+        <v>100</v>
+      </c>
+      <c r="M20" s="70"/>
+      <c r="N20" s="4">
+        <v>46098</v>
+      </c>
+      <c r="O20" s="78" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" ht="24" customHeight="1">
       <c r="B21" s="4">
         <v>46008</v>
       </c>
@@ -4959,8 +6120,27 @@
       <c r="H21" s="36">
         <v>100</v>
       </c>
-    </row>
-    <row r="22" spans="2:8" ht="24" customHeight="1">
+      <c r="J21" s="4">
+        <v>46072</v>
+      </c>
+      <c r="K21" s="60" t="s">
+        <v>5</v>
+      </c>
+      <c r="L21" s="25">
+        <v>100</v>
+      </c>
+      <c r="M21" s="70"/>
+      <c r="N21" s="4">
+        <v>46099</v>
+      </c>
+      <c r="O21" s="79" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" ht="24" customHeight="1">
       <c r="B22" s="4">
         <v>46009</v>
       </c>
@@ -4979,8 +6159,27 @@
       <c r="H22" s="36">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="2:8" ht="24" customHeight="1">
+      <c r="J22" s="4">
+        <v>46073</v>
+      </c>
+      <c r="K22" s="61" t="s">
+        <v>5</v>
+      </c>
+      <c r="L22" s="25">
+        <v>100</v>
+      </c>
+      <c r="M22" s="70"/>
+      <c r="N22" s="4">
+        <v>46100</v>
+      </c>
+      <c r="O22" s="80" t="s">
+        <v>5</v>
+      </c>
+      <c r="P22" s="80">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" ht="24" customHeight="1">
       <c r="B23" s="4">
         <v>46010</v>
       </c>
@@ -4999,8 +6198,27 @@
       <c r="H23" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="24" spans="2:8" ht="24" customHeight="1">
+      <c r="J23" s="4">
+        <v>46074</v>
+      </c>
+      <c r="K23" s="61" t="s">
+        <v>10</v>
+      </c>
+      <c r="L23" s="61" t="s">
+        <v>10</v>
+      </c>
+      <c r="M23" s="70"/>
+      <c r="N23" s="4">
+        <v>46101</v>
+      </c>
+      <c r="O23" s="80" t="s">
+        <v>5</v>
+      </c>
+      <c r="P23" s="80">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17" ht="24" customHeight="1">
       <c r="B24" s="4">
         <v>46011</v>
       </c>
@@ -5019,8 +6237,27 @@
       <c r="H24" s="38">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="2:8" ht="24" customHeight="1">
+      <c r="J24" s="4">
+        <v>46075</v>
+      </c>
+      <c r="K24" s="62" t="s">
+        <v>5</v>
+      </c>
+      <c r="L24" s="25">
+        <v>100</v>
+      </c>
+      <c r="M24" s="70"/>
+      <c r="N24" s="4">
+        <v>46102</v>
+      </c>
+      <c r="O24" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="P24" s="81" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" ht="24" customHeight="1">
       <c r="B25" s="4">
         <v>46012</v>
       </c>
@@ -5039,8 +6276,27 @@
       <c r="H25" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="26" spans="2:8" ht="24" customHeight="1">
+      <c r="J25" s="4">
+        <v>46076</v>
+      </c>
+      <c r="K25" s="62" t="s">
+        <v>5</v>
+      </c>
+      <c r="L25" s="25">
+        <v>100</v>
+      </c>
+      <c r="M25" s="70"/>
+      <c r="N25" s="4">
+        <v>46103</v>
+      </c>
+      <c r="O25" s="81" t="s">
+        <v>5</v>
+      </c>
+      <c r="P25" s="25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" ht="24" customHeight="1">
       <c r="B26" s="4">
         <v>46013</v>
       </c>
@@ -5050,8 +6306,39 @@
       <c r="D26" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="27" spans="2:8" ht="24" customHeight="1">
+      <c r="F26" s="4">
+        <v>46046</v>
+      </c>
+      <c r="G26" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="H26" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="J26" s="4">
+        <v>46077</v>
+      </c>
+      <c r="K26" s="64" t="s">
+        <v>5</v>
+      </c>
+      <c r="L26" s="25">
+        <v>100</v>
+      </c>
+      <c r="M26" s="70"/>
+      <c r="N26" s="84">
+        <v>46104</v>
+      </c>
+      <c r="O26" s="83" t="s">
+        <v>28</v>
+      </c>
+      <c r="P26" s="83" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q26" s="83">
+        <v>-350</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" ht="24" customHeight="1">
       <c r="B27" s="4">
         <v>46014</v>
       </c>
@@ -5061,8 +6348,36 @@
       <c r="D27" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="28" spans="2:8" ht="24" customHeight="1">
+      <c r="F27" s="4">
+        <v>46047</v>
+      </c>
+      <c r="G27" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="H27" s="25">
+        <v>100</v>
+      </c>
+      <c r="J27" s="4">
+        <v>46078</v>
+      </c>
+      <c r="K27" s="67" t="s">
+        <v>5</v>
+      </c>
+      <c r="L27" s="25">
+        <v>100</v>
+      </c>
+      <c r="M27" s="70"/>
+      <c r="N27" s="4">
+        <v>46105</v>
+      </c>
+      <c r="O27" s="82" t="s">
+        <v>5</v>
+      </c>
+      <c r="P27" s="82">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17" ht="24" customHeight="1">
       <c r="B28" s="4">
         <v>46015</v>
       </c>
@@ -5072,8 +6387,36 @@
       <c r="D28" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="29" spans="2:8" ht="24" customHeight="1">
+      <c r="F28" s="4">
+        <v>46048</v>
+      </c>
+      <c r="G28" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="H28" s="42">
+        <v>100</v>
+      </c>
+      <c r="J28" s="4">
+        <v>46079</v>
+      </c>
+      <c r="K28" s="67" t="s">
+        <v>28</v>
+      </c>
+      <c r="L28" s="67" t="s">
+        <v>28</v>
+      </c>
+      <c r="M28" s="70"/>
+      <c r="N28" s="4">
+        <v>46106</v>
+      </c>
+      <c r="O28" s="85" t="s">
+        <v>5</v>
+      </c>
+      <c r="P28" s="25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17" ht="24" customHeight="1">
       <c r="B29" s="4">
         <v>46016</v>
       </c>
@@ -5083,8 +6426,36 @@
       <c r="D29" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="30" spans="2:8" ht="24" customHeight="1">
+      <c r="F29" s="4">
+        <v>46049</v>
+      </c>
+      <c r="G29" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="H29" s="43">
+        <v>100</v>
+      </c>
+      <c r="J29" s="4">
+        <v>46080</v>
+      </c>
+      <c r="K29" s="68" t="s">
+        <v>28</v>
+      </c>
+      <c r="L29" s="68" t="s">
+        <v>28</v>
+      </c>
+      <c r="M29" s="70"/>
+      <c r="N29" s="4">
+        <v>46107</v>
+      </c>
+      <c r="O29" s="86" t="s">
+        <v>5</v>
+      </c>
+      <c r="P29" s="25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17" ht="24" customHeight="1">
       <c r="B30" s="4">
         <v>46017</v>
       </c>
@@ -5094,8 +6465,36 @@
       <c r="D30" s="25" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="31" spans="2:8" ht="24" customHeight="1">
+      <c r="F30" s="4">
+        <v>46050</v>
+      </c>
+      <c r="G30" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="H30" s="43">
+        <v>100</v>
+      </c>
+      <c r="J30" s="4">
+        <v>46081</v>
+      </c>
+      <c r="K30" s="69" t="s">
+        <v>28</v>
+      </c>
+      <c r="L30" s="69" t="s">
+        <v>28</v>
+      </c>
+      <c r="M30" s="70"/>
+      <c r="N30" s="4">
+        <v>46108</v>
+      </c>
+      <c r="O30" s="86" t="s">
+        <v>5</v>
+      </c>
+      <c r="P30" s="25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17" ht="24" customHeight="1">
       <c r="B31" s="4">
         <v>46018</v>
       </c>
@@ -5105,8 +6504,36 @@
       <c r="D31" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="32" spans="2:8" ht="24" customHeight="1">
+      <c r="F31" s="4">
+        <v>46051</v>
+      </c>
+      <c r="G31" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="H31" s="44">
+        <v>100</v>
+      </c>
+      <c r="J31" s="4">
+        <v>46082</v>
+      </c>
+      <c r="K31" s="69" t="s">
+        <v>28</v>
+      </c>
+      <c r="L31" s="69" t="s">
+        <v>28</v>
+      </c>
+      <c r="M31" s="70"/>
+      <c r="N31" s="4">
+        <v>46109</v>
+      </c>
+      <c r="O31" s="86" t="s">
+        <v>31</v>
+      </c>
+      <c r="P31" s="86" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="2:17" ht="24" customHeight="1">
       <c r="B32" s="4">
         <v>46019</v>
       </c>
@@ -5116,8 +6543,32 @@
       <c r="D32" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="33" spans="2:4" ht="24" customHeight="1">
+      <c r="F32" s="4">
+        <v>46052</v>
+      </c>
+      <c r="G32" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="44">
+        <v>100</v>
+      </c>
+      <c r="J32" s="1">
+        <v>46084</v>
+      </c>
+      <c r="L32" s="25">
+        <v>8150</v>
+      </c>
+      <c r="N32" s="4">
+        <v>46110</v>
+      </c>
+      <c r="O32" s="88" t="s">
+        <v>5</v>
+      </c>
+      <c r="P32" s="25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" ht="24" customHeight="1">
       <c r="B33" s="4">
         <v>46020</v>
       </c>
@@ -5127,8 +6578,17 @@
       <c r="D33" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="34" spans="2:4" ht="24" customHeight="1">
+      <c r="F33" s="4">
+        <v>46053</v>
+      </c>
+      <c r="G33" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="H33" s="44" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" ht="24" customHeight="1">
       <c r="B34" s="4">
         <v>46021</v>
       </c>
@@ -5138,8 +6598,17 @@
       <c r="D34" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="35" spans="2:4" ht="24" customHeight="1">
+      <c r="F34" s="4">
+        <v>46054</v>
+      </c>
+      <c r="G34" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="H34" s="44">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" ht="24" customHeight="1">
       <c r="B35" s="4">
         <v>46022</v>
       </c>
@@ -5149,8 +6618,17 @@
       <c r="D35" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="36" spans="2:4" ht="24" customHeight="1">
+      <c r="F35" s="4">
+        <v>46055</v>
+      </c>
+      <c r="G35" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="H35" s="44">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" ht="24" customHeight="1">
       <c r="B36" s="4">
         <v>46023</v>
       </c>
@@ -5160,8 +6638,17 @@
       <c r="D36" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="37" spans="2:4" ht="24" customHeight="1">
+      <c r="F36" s="4">
+        <v>46057</v>
+      </c>
+      <c r="G36" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="H36" s="25">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" ht="24" customHeight="1">
       <c r="B37" s="4">
         <v>46024</v>
       </c>
@@ -5172,7 +6659,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="2:4" ht="24" customHeight="1">
+    <row r="38" spans="2:8" ht="24" customHeight="1">
       <c r="B38" s="4">
         <v>46025</v>
       </c>
@@ -5184,11 +6671,15 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="8">
+    <mergeCell ref="N2:N4"/>
+    <mergeCell ref="O2:P3"/>
+    <mergeCell ref="K2:L3"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="C2:D3"/>
     <mergeCell ref="F2:F4"/>
     <mergeCell ref="G2:H3"/>
+    <mergeCell ref="J2:J4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5197,60 +6688,85 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:M36"/>
+  <dimension ref="A2:Q36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="17.5703125" defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="16384" width="17.5703125" style="29"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" ht="24" customHeight="1">
-      <c r="B2" s="48"/>
-      <c r="C2" s="42">
+    <row r="2" spans="1:17" ht="24" customHeight="1">
+      <c r="B2" s="96"/>
+      <c r="C2" s="90">
         <f>SUM(D5:D44)</f>
         <v>10500</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="42">
+      <c r="D2" s="90"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="90">
         <f>SUM(H5:H44)</f>
-        <v>420</v>
-      </c>
-      <c r="H2" s="42"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-    </row>
-    <row r="3" spans="1:13" ht="24" customHeight="1">
-      <c r="B3" s="48"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
-    </row>
-    <row r="4" spans="1:13" ht="24" customHeight="1">
-      <c r="B4" s="48"/>
+        <v>10500</v>
+      </c>
+      <c r="H2" s="90"/>
+      <c r="K2" s="96"/>
+      <c r="L2" s="90">
+        <f>SUM(M5:M37)</f>
+        <v>5250</v>
+      </c>
+      <c r="M2" s="90"/>
+      <c r="O2" s="96">
+        <v>3</v>
+      </c>
+      <c r="P2" s="90">
+        <f>SUM(Q5:Q37)</f>
+        <v>360</v>
+      </c>
+      <c r="Q2" s="90"/>
+    </row>
+    <row r="3" spans="1:17" ht="24" customHeight="1">
+      <c r="B3" s="96"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
+      <c r="K3" s="96"/>
+      <c r="L3" s="90"/>
+      <c r="M3" s="90"/>
+      <c r="O3" s="96"/>
+      <c r="P3" s="90"/>
+      <c r="Q3" s="90"/>
+    </row>
+    <row r="4" spans="1:17" ht="24" customHeight="1">
+      <c r="B4" s="96"/>
       <c r="C4" s="28" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="48"/>
+      <c r="F4" s="96"/>
       <c r="G4" s="33" t="s">
         <v>0</v>
       </c>
       <c r="H4" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="48"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
-    </row>
-    <row r="5" spans="1:13" ht="24" customHeight="1">
+      <c r="K4" s="96"/>
+      <c r="L4" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="M4" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4" s="96"/>
+      <c r="P4" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="71" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="24" customHeight="1">
       <c r="B5" s="31">
         <v>46006</v>
       </c>
@@ -5261,7 +6777,7 @@
         <v>60</v>
       </c>
       <c r="F5" s="31">
-        <v>45672</v>
+        <v>46037</v>
       </c>
       <c r="G5" s="32" t="s">
         <v>5</v>
@@ -5269,8 +6785,26 @@
       <c r="H5" s="32">
         <v>60</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" customHeight="1">
+      <c r="K5" s="4">
+        <v>46068</v>
+      </c>
+      <c r="L5" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="O5" s="4">
+        <v>46083</v>
+      </c>
+      <c r="P5" s="72" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q5" s="72" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="24" customHeight="1">
       <c r="A6" s="30"/>
       <c r="B6" s="31">
         <v>46007</v>
@@ -5282,7 +6816,7 @@
         <v>60</v>
       </c>
       <c r="F6" s="31">
-        <v>45673</v>
+        <v>46038</v>
       </c>
       <c r="G6" s="32" t="s">
         <v>10</v>
@@ -5290,8 +6824,27 @@
       <c r="H6" s="35" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="24" customHeight="1">
+      <c r="K6" s="4">
+        <v>46069</v>
+      </c>
+      <c r="L6" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="M6" s="29">
+        <v>60</v>
+      </c>
+      <c r="N6" s="70"/>
+      <c r="O6" s="4">
+        <v>46084</v>
+      </c>
+      <c r="P6" s="72" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q6" s="29">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="24" customHeight="1">
       <c r="A7" s="30"/>
       <c r="B7" s="31">
         <v>46008</v>
@@ -5303,7 +6856,7 @@
         <v>60</v>
       </c>
       <c r="F7" s="31">
-        <v>45674</v>
+        <v>46039</v>
       </c>
       <c r="G7" s="32" t="s">
         <v>5</v>
@@ -5311,8 +6864,27 @@
       <c r="H7" s="29">
         <v>60</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" customHeight="1">
+      <c r="K7" s="4">
+        <v>46070</v>
+      </c>
+      <c r="L7" s="59" t="s">
+        <v>28</v>
+      </c>
+      <c r="M7" s="59" t="s">
+        <v>28</v>
+      </c>
+      <c r="N7" s="70"/>
+      <c r="O7" s="4">
+        <v>46105</v>
+      </c>
+      <c r="P7" s="82" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q7" s="82">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="24" customHeight="1">
       <c r="A8" s="30"/>
       <c r="B8" s="31">
         <v>46009</v>
@@ -5324,7 +6896,7 @@
         <v>60</v>
       </c>
       <c r="F8" s="31">
-        <v>45675</v>
+        <v>46040</v>
       </c>
       <c r="G8" s="32" t="s">
         <v>5</v>
@@ -5332,8 +6904,27 @@
       <c r="H8" s="36">
         <v>60</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="24" customHeight="1">
+      <c r="K8" s="4">
+        <v>46071</v>
+      </c>
+      <c r="L8" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="M8" s="29">
+        <v>60</v>
+      </c>
+      <c r="N8" s="70"/>
+      <c r="O8" s="4">
+        <v>46106</v>
+      </c>
+      <c r="P8" s="82" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="82">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="24" customHeight="1">
       <c r="A9" s="30"/>
       <c r="B9" s="31">
         <v>46010</v>
@@ -5345,7 +6936,7 @@
         <v>28</v>
       </c>
       <c r="F9" s="31">
-        <v>45676</v>
+        <v>46041</v>
       </c>
       <c r="G9" s="32" t="s">
         <v>5</v>
@@ -5353,8 +6944,27 @@
       <c r="H9" s="36">
         <v>60</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="24" customHeight="1">
+      <c r="K9" s="4">
+        <v>46072</v>
+      </c>
+      <c r="L9" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="M9" s="29">
+        <v>60</v>
+      </c>
+      <c r="N9" s="70"/>
+      <c r="O9" s="4">
+        <v>46107</v>
+      </c>
+      <c r="P9" s="86" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="75">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="24" customHeight="1">
       <c r="A10" s="30"/>
       <c r="B10" s="31">
         <v>46011</v>
@@ -5366,7 +6976,7 @@
         <v>60</v>
       </c>
       <c r="F10" s="31">
-        <v>45677</v>
+        <v>46042</v>
       </c>
       <c r="G10" s="36" t="s">
         <v>28</v>
@@ -5374,8 +6984,27 @@
       <c r="H10" s="36" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="24" customHeight="1">
+      <c r="K10" s="4">
+        <v>46073</v>
+      </c>
+      <c r="L10" s="60" t="s">
+        <v>28</v>
+      </c>
+      <c r="M10" s="60" t="s">
+        <v>28</v>
+      </c>
+      <c r="N10" s="70"/>
+      <c r="O10" s="4">
+        <v>46108</v>
+      </c>
+      <c r="P10" s="86" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q10" s="86" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="24" customHeight="1">
       <c r="A11" s="30"/>
       <c r="B11" s="31">
         <v>46012</v>
@@ -5387,7 +7016,7 @@
         <v>60</v>
       </c>
       <c r="F11" s="31">
-        <v>45678</v>
+        <v>46043</v>
       </c>
       <c r="G11" s="37" t="s">
         <v>5</v>
@@ -5395,8 +7024,27 @@
       <c r="H11" s="29">
         <v>60</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="24" customHeight="1">
+      <c r="K11" s="4">
+        <v>46074</v>
+      </c>
+      <c r="L11" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="M11" s="29">
+        <v>60</v>
+      </c>
+      <c r="N11" s="70"/>
+      <c r="O11" s="4">
+        <v>46109</v>
+      </c>
+      <c r="P11" s="86" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="76">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="24" customHeight="1">
       <c r="A12" s="30"/>
       <c r="B12" s="31">
         <v>46013</v>
@@ -5408,7 +7056,7 @@
         <v>60</v>
       </c>
       <c r="F12" s="31">
-        <v>45679</v>
+        <v>46044</v>
       </c>
       <c r="G12" s="38" t="s">
         <v>5</v>
@@ -5416,8 +7064,27 @@
       <c r="H12" s="29">
         <v>60</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="24" customHeight="1">
+      <c r="K12" s="4">
+        <v>46075</v>
+      </c>
+      <c r="L12" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="M12" s="62">
+        <v>60</v>
+      </c>
+      <c r="N12" s="70"/>
+      <c r="O12" s="4">
+        <v>46110</v>
+      </c>
+      <c r="P12" s="87" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="77">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="24" customHeight="1">
       <c r="A13" s="30"/>
       <c r="B13" s="31">
         <v>46014</v>
@@ -5429,7 +7096,7 @@
         <v>60</v>
       </c>
       <c r="F13" s="31">
-        <v>45680</v>
+        <v>46045</v>
       </c>
       <c r="G13" s="39" t="s">
         <v>28</v>
@@ -5437,8 +7104,21 @@
       <c r="H13" s="39" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" ht="24" customHeight="1">
+      <c r="K13" s="4">
+        <v>46076</v>
+      </c>
+      <c r="L13" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="M13" s="62">
+        <v>60</v>
+      </c>
+      <c r="N13" s="70"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="77"/>
+      <c r="Q13" s="77"/>
+    </row>
+    <row r="14" spans="1:17" ht="24" customHeight="1">
       <c r="A14" s="30"/>
       <c r="B14" s="31">
         <v>46015</v>
@@ -5450,7 +7130,7 @@
         <v>60</v>
       </c>
       <c r="F14" s="31">
-        <v>45681</v>
+        <v>46046</v>
       </c>
       <c r="G14" s="40" t="s">
         <v>5</v>
@@ -5458,8 +7138,21 @@
       <c r="H14" s="29">
         <v>60</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" ht="24" customHeight="1">
+      <c r="K14" s="4">
+        <v>46077</v>
+      </c>
+      <c r="L14" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="M14" s="29">
+        <v>60</v>
+      </c>
+      <c r="N14" s="70"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="77"/>
+      <c r="Q14" s="77"/>
+    </row>
+    <row r="15" spans="1:17" ht="24" customHeight="1">
       <c r="A15" s="30"/>
       <c r="B15" s="31">
         <v>46016</v>
@@ -5470,9 +7163,30 @@
       <c r="D15" s="32">
         <v>60</v>
       </c>
-      <c r="F15" s="4"/>
-    </row>
-    <row r="16" spans="1:13" ht="24" customHeight="1">
+      <c r="F15" s="31">
+        <v>46047</v>
+      </c>
+      <c r="G15" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="H15" s="42">
+        <v>60</v>
+      </c>
+      <c r="K15" s="4">
+        <v>46078</v>
+      </c>
+      <c r="L15" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="M15" s="29">
+        <v>60</v>
+      </c>
+      <c r="N15" s="70"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="77"/>
+      <c r="Q15" s="77"/>
+    </row>
+    <row r="16" spans="1:17" ht="24" customHeight="1">
       <c r="A16" s="30"/>
       <c r="B16" s="31">
         <v>46017</v>
@@ -5483,8 +7197,30 @@
       <c r="D16" s="32" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" ht="21">
+      <c r="F16" s="31">
+        <v>46048</v>
+      </c>
+      <c r="G16" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="H16" s="42">
+        <v>60</v>
+      </c>
+      <c r="K16" s="4">
+        <v>46079</v>
+      </c>
+      <c r="L16" s="67" t="s">
+        <v>28</v>
+      </c>
+      <c r="M16" s="67" t="s">
+        <v>28</v>
+      </c>
+      <c r="N16" s="70"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="77"/>
+      <c r="Q16" s="77"/>
+    </row>
+    <row r="17" spans="1:17" ht="21">
       <c r="A17" s="30"/>
       <c r="B17" s="31">
         <v>46018</v>
@@ -5495,8 +7231,30 @@
       <c r="D17" s="32">
         <v>60</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" ht="21">
+      <c r="F17" s="31">
+        <v>46049</v>
+      </c>
+      <c r="G17" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" s="43">
+        <v>60</v>
+      </c>
+      <c r="K17" s="4">
+        <v>46080</v>
+      </c>
+      <c r="L17" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="M17" s="29">
+        <v>60</v>
+      </c>
+      <c r="N17" s="70"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="77"/>
+      <c r="Q17" s="77"/>
+    </row>
+    <row r="18" spans="1:17" ht="21">
       <c r="A18" s="30"/>
       <c r="B18" s="31">
         <v>46019</v>
@@ -5507,9 +7265,27 @@
       <c r="D18" s="32">
         <v>60</v>
       </c>
-      <c r="F18" s="4"/>
-    </row>
-    <row r="19" spans="1:9" ht="21">
+      <c r="F18" s="31">
+        <v>46050</v>
+      </c>
+      <c r="G18" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="43">
+        <v>60</v>
+      </c>
+      <c r="K18" s="4">
+        <v>46081</v>
+      </c>
+      <c r="L18" s="69" t="s">
+        <v>10</v>
+      </c>
+      <c r="M18" s="69" t="s">
+        <v>10</v>
+      </c>
+      <c r="N18" s="70"/>
+    </row>
+    <row r="19" spans="1:17" ht="21">
       <c r="A19" s="30"/>
       <c r="B19" s="31">
         <v>46020</v>
@@ -5520,8 +7296,27 @@
       <c r="D19" s="32">
         <v>60</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" ht="21">
+      <c r="F19" s="31">
+        <v>46051</v>
+      </c>
+      <c r="G19" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="H19" s="44">
+        <v>60</v>
+      </c>
+      <c r="K19" s="4">
+        <v>46082</v>
+      </c>
+      <c r="L19" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="M19" s="29">
+        <v>60</v>
+      </c>
+      <c r="N19" s="70"/>
+    </row>
+    <row r="20" spans="1:17" ht="21">
       <c r="A20" s="30"/>
       <c r="B20" s="31">
         <v>46021</v>
@@ -5532,8 +7327,23 @@
       <c r="D20" s="32">
         <v>60</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" ht="21">
+      <c r="F20" s="31">
+        <v>46052</v>
+      </c>
+      <c r="G20" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="H20" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="K20" s="1">
+        <v>46084</v>
+      </c>
+      <c r="M20" s="29">
+        <v>4650</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="21">
       <c r="A21" s="30"/>
       <c r="B21" s="31">
         <v>46022</v>
@@ -5544,11 +7354,18 @@
       <c r="D21" s="32">
         <v>60</v>
       </c>
-      <c r="G21" s="49"/>
-      <c r="H21" s="49"/>
-      <c r="I21" s="49"/>
-    </row>
-    <row r="22" spans="1:9" ht="21">
+      <c r="F21" s="31">
+        <v>46053</v>
+      </c>
+      <c r="G21" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="H21" s="44">
+        <v>60</v>
+      </c>
+      <c r="I21" s="97"/>
+    </row>
+    <row r="22" spans="1:17" ht="21">
       <c r="A22" s="30"/>
       <c r="B22" s="31">
         <v>46023</v>
@@ -5559,11 +7376,18 @@
       <c r="D22" s="32">
         <v>60</v>
       </c>
-      <c r="G22" s="49"/>
-      <c r="H22" s="49"/>
-      <c r="I22" s="49"/>
-    </row>
-    <row r="23" spans="1:9" ht="21">
+      <c r="F22" s="31">
+        <v>46054</v>
+      </c>
+      <c r="G22" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="44">
+        <v>60</v>
+      </c>
+      <c r="I22" s="97"/>
+    </row>
+    <row r="23" spans="1:17" ht="21">
       <c r="A23" s="30"/>
       <c r="B23" s="31">
         <v>46024</v>
@@ -5574,8 +7398,17 @@
       <c r="D23" s="32" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" ht="21">
+      <c r="F23" s="31">
+        <v>46055</v>
+      </c>
+      <c r="G23" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="H23" s="44">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="21">
       <c r="A24" s="30"/>
       <c r="B24" s="31">
         <v>46025</v>
@@ -5586,8 +7419,17 @@
       <c r="D24" s="32">
         <v>60</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" ht="21">
+      <c r="F24" s="31">
+        <v>46056</v>
+      </c>
+      <c r="G24" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="44">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="21">
       <c r="A25" s="30"/>
       <c r="B25" s="31">
         <v>46026</v>
@@ -5598,8 +7440,17 @@
       <c r="D25" s="29">
         <v>60</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" ht="21">
+      <c r="F25" s="31">
+        <v>46057</v>
+      </c>
+      <c r="G25" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="H25" s="46">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="21">
       <c r="A26" s="30"/>
       <c r="B26" s="31">
         <v>46027</v>
@@ -5610,8 +7461,17 @@
       <c r="D26" s="29">
         <v>60</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" ht="21">
+      <c r="F26" s="31">
+        <v>46058</v>
+      </c>
+      <c r="G26" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" s="48">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="21">
       <c r="A27" s="30"/>
       <c r="B27" s="31">
         <v>46028</v>
@@ -5622,8 +7482,17 @@
       <c r="D27" s="29" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" ht="21">
+      <c r="F27" s="31">
+        <v>46059</v>
+      </c>
+      <c r="G27" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="H27" s="48" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="21">
       <c r="A28" s="30"/>
       <c r="B28" s="31">
         <v>46029</v>
@@ -5634,8 +7503,17 @@
       <c r="D28" s="29">
         <v>60</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" ht="21">
+      <c r="F28" s="31">
+        <v>46060</v>
+      </c>
+      <c r="G28" s="50" t="s">
+        <v>5</v>
+      </c>
+      <c r="H28" s="29">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="21">
       <c r="A29" s="30"/>
       <c r="B29" s="31">
         <v>46030</v>
@@ -5646,8 +7524,17 @@
       <c r="D29" s="29">
         <v>60</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" ht="24" customHeight="1">
+      <c r="F29" s="31">
+        <v>46061</v>
+      </c>
+      <c r="G29" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29" s="50" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="24" customHeight="1">
       <c r="A30" s="30"/>
       <c r="B30" s="31">
         <v>46031</v>
@@ -5658,8 +7545,17 @@
       <c r="D30" s="29" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" ht="24" customHeight="1">
+      <c r="F30" s="31">
+        <v>46062</v>
+      </c>
+      <c r="G30" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="H30" s="51" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="24" customHeight="1">
       <c r="A31" s="30"/>
       <c r="B31" s="31">
         <v>46032</v>
@@ -5670,8 +7566,17 @@
       <c r="D31" s="29">
         <v>60</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" ht="24" customHeight="1">
+      <c r="F31" s="31">
+        <v>46063</v>
+      </c>
+      <c r="G31" s="52" t="s">
+        <v>10</v>
+      </c>
+      <c r="H31" s="52" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="24" customHeight="1">
       <c r="A32" s="30"/>
       <c r="B32" s="31">
         <v>46033</v>
@@ -5682,8 +7587,17 @@
       <c r="D32" s="29">
         <v>60</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" ht="24" customHeight="1">
+      <c r="F32" s="31">
+        <v>46064</v>
+      </c>
+      <c r="G32" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="H32" s="53" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="24" customHeight="1">
       <c r="A33" s="30"/>
       <c r="B33" s="31">
         <v>46034</v>
@@ -5694,8 +7608,17 @@
       <c r="D33" s="29">
         <v>60</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" ht="24" customHeight="1">
+      <c r="F33" s="31">
+        <v>46065</v>
+      </c>
+      <c r="G33" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="H33" s="53" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="24" customHeight="1">
       <c r="A34" s="30"/>
       <c r="B34" s="31">
         <v>46035</v>
@@ -5706,8 +7629,17 @@
       <c r="D34" s="30">
         <v>60</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" ht="24" customHeight="1">
+      <c r="F34" s="31">
+        <v>46066</v>
+      </c>
+      <c r="G34" s="54" t="s">
+        <v>10</v>
+      </c>
+      <c r="H34" s="54" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="24" customHeight="1">
       <c r="A35" s="30"/>
       <c r="B35" s="31">
         <v>46036</v>
@@ -5718,8 +7650,17 @@
       <c r="D35" s="30">
         <v>60</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" ht="24" customHeight="1">
+      <c r="F35" s="31">
+        <v>46067</v>
+      </c>
+      <c r="G35" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" s="55" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="24" customHeight="1">
       <c r="B36" s="31">
         <v>46038</v>
       </c>
@@ -5729,12 +7670,21 @@
       <c r="D36" s="29">
         <v>8940</v>
       </c>
+      <c r="F36" s="31">
+        <v>46071</v>
+      </c>
+      <c r="G36" s="59" t="s">
+        <v>16</v>
+      </c>
+      <c r="H36" s="55">
+        <v>9360</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="O2:O4"/>
+    <mergeCell ref="P2:Q3"/>
     <mergeCell ref="L2:M3"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="H21:H22"/>
     <mergeCell ref="I21:I22"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="C2:D3"/>

--- a/BEDEL(2).xlsx
+++ b/BEDEL(2).xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="34">
   <si>
     <t>Description</t>
   </si>
@@ -122,12 +122,18 @@
   <si>
     <t>dimas</t>
   </si>
+  <si>
+    <t>Deduction</t>
+  </si>
+  <si>
+    <t>dimass</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -222,6 +228,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -231,7 +244,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -254,11 +267,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -524,6 +574,45 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -546,6 +635,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -857,40 +955,40 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="17.5703125" defaultRowHeight="24" customHeight="1"/>
   <sheetData>
     <row r="2" spans="2:8" ht="24" customHeight="1">
-      <c r="B2" s="89" t="s">
+      <c r="B2" s="102" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="90">
+      <c r="C2" s="103">
         <f>SUM(D5:D14)</f>
         <v>700</v>
       </c>
-      <c r="D2" s="90"/>
-      <c r="F2" s="91">
+      <c r="D2" s="103"/>
+      <c r="F2" s="104">
         <v>9</v>
       </c>
-      <c r="G2" s="90">
+      <c r="G2" s="103">
         <f>SUM(H5:H35)</f>
         <v>2175</v>
       </c>
-      <c r="H2" s="90"/>
+      <c r="H2" s="103"/>
     </row>
     <row r="3" spans="2:8" ht="24" customHeight="1">
-      <c r="B3" s="89"/>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="F3" s="91"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
+      <c r="B3" s="102"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="103"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="103"/>
+      <c r="H3" s="103"/>
     </row>
     <row r="4" spans="2:8" ht="24" customHeight="1">
-      <c r="B4" s="89"/>
+      <c r="B4" s="102"/>
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="91"/>
+      <c r="F4" s="104"/>
       <c r="G4" s="8" t="s">
         <v>0</v>
       </c>
@@ -1333,20 +1431,20 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="17.5703125" defaultRowHeight="24" customHeight="1"/>
   <sheetData>
     <row r="2" spans="1:4" ht="24" customHeight="1">
-      <c r="B2" s="91"/>
-      <c r="C2" s="90">
+      <c r="B2" s="104"/>
+      <c r="C2" s="103">
         <f>SUM(D5:D31)</f>
         <v>2400</v>
       </c>
-      <c r="D2" s="90"/>
+      <c r="D2" s="103"/>
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
-      <c r="B3" s="91"/>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
+      <c r="B3" s="104"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="103"/>
     </row>
     <row r="4" spans="1:4" ht="24" customHeight="1">
-      <c r="B4" s="91"/>
+      <c r="B4" s="104"/>
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
@@ -1558,58 +1656,58 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="24" customHeight="1">
-      <c r="B2" s="92">
+      <c r="B2" s="105">
         <v>7</v>
       </c>
-      <c r="C2" s="93">
+      <c r="C2" s="106">
         <f>SUM(D5:D7)</f>
         <v>8500</v>
       </c>
-      <c r="D2" s="93"/>
-      <c r="F2" s="92">
+      <c r="D2" s="106"/>
+      <c r="F2" s="105">
         <v>8</v>
       </c>
-      <c r="G2" s="93">
+      <c r="G2" s="106">
         <f>SUM(H5:H7)</f>
         <v>8500</v>
       </c>
-      <c r="H2" s="93"/>
-      <c r="J2" s="92">
+      <c r="H2" s="106"/>
+      <c r="J2" s="105">
         <v>9</v>
       </c>
-      <c r="K2" s="93">
+      <c r="K2" s="106">
         <f>SUM(L5:L7)</f>
         <v>1500</v>
       </c>
-      <c r="L2" s="93"/>
+      <c r="L2" s="106"/>
     </row>
     <row r="3" spans="2:12" ht="24" customHeight="1">
-      <c r="B3" s="92"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="J3" s="92"/>
-      <c r="K3" s="93"/>
-      <c r="L3" s="93"/>
+      <c r="B3" s="105"/>
+      <c r="C3" s="106"/>
+      <c r="D3" s="106"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="106"/>
+      <c r="H3" s="106"/>
+      <c r="J3" s="105"/>
+      <c r="K3" s="106"/>
+      <c r="L3" s="106"/>
     </row>
     <row r="4" spans="2:12" ht="24" customHeight="1">
-      <c r="B4" s="92"/>
+      <c r="B4" s="105"/>
       <c r="C4" s="9" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="92"/>
+      <c r="F4" s="105"/>
       <c r="G4" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="J4" s="92"/>
+      <c r="J4" s="105"/>
       <c r="K4" s="9" t="s">
         <v>0</v>
       </c>
@@ -1680,56 +1778,56 @@
       <c r="F9" s="10"/>
     </row>
     <row r="10" spans="2:12" ht="24" customHeight="1">
-      <c r="B10" s="92">
+      <c r="B10" s="105">
         <v>10</v>
       </c>
-      <c r="C10" s="93">
+      <c r="C10" s="106">
         <f>SUM(D13:D39)</f>
         <v>8500</v>
       </c>
-      <c r="D10" s="93"/>
-      <c r="F10" s="92">
+      <c r="D10" s="106"/>
+      <c r="F10" s="105">
         <v>11</v>
       </c>
-      <c r="G10" s="93">
+      <c r="G10" s="106">
         <f>SUM(H13:H45)</f>
         <v>8500</v>
       </c>
-      <c r="H10" s="93"/>
-      <c r="J10" s="92"/>
-      <c r="K10" s="93">
+      <c r="H10" s="106"/>
+      <c r="J10" s="105"/>
+      <c r="K10" s="106">
         <f>SUM(L13:L44)</f>
         <v>4400</v>
       </c>
-      <c r="L10" s="93"/>
+      <c r="L10" s="106"/>
     </row>
     <row r="11" spans="2:12" ht="24" customHeight="1">
-      <c r="B11" s="92"/>
-      <c r="C11" s="93"/>
-      <c r="D11" s="93"/>
-      <c r="F11" s="92"/>
-      <c r="G11" s="93"/>
-      <c r="H11" s="93"/>
-      <c r="J11" s="92"/>
-      <c r="K11" s="93"/>
-      <c r="L11" s="93"/>
+      <c r="B11" s="105"/>
+      <c r="C11" s="106"/>
+      <c r="D11" s="106"/>
+      <c r="F11" s="105"/>
+      <c r="G11" s="106"/>
+      <c r="H11" s="106"/>
+      <c r="J11" s="105"/>
+      <c r="K11" s="106"/>
+      <c r="L11" s="106"/>
     </row>
     <row r="12" spans="2:12" ht="24" customHeight="1">
-      <c r="B12" s="92"/>
+      <c r="B12" s="105"/>
       <c r="C12" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D12" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F12" s="92"/>
+      <c r="F12" s="105"/>
       <c r="G12" s="16" t="s">
         <v>0</v>
       </c>
       <c r="H12" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="J12" s="92"/>
+      <c r="J12" s="105"/>
       <c r="K12" s="19" t="s">
         <v>0</v>
       </c>
@@ -2333,155 +2431,155 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:AF61"/>
+  <dimension ref="B2:AF62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="17.5703125" defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="16384" width="17.5703125" style="2"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:32" ht="24" customHeight="1">
-      <c r="B2" s="95">
+      <c r="B2" s="108">
         <v>6</v>
       </c>
-      <c r="C2" s="94">
+      <c r="C2" s="107">
         <f>SUM(D5:D31)</f>
         <v>13000</v>
       </c>
-      <c r="D2" s="94"/>
-      <c r="F2" s="95">
+      <c r="D2" s="107"/>
+      <c r="F2" s="108">
         <v>7</v>
       </c>
-      <c r="G2" s="94">
+      <c r="G2" s="107">
         <f>SUM(H5:H32)</f>
         <v>13000</v>
       </c>
-      <c r="H2" s="94"/>
-      <c r="J2" s="95">
+      <c r="H2" s="107"/>
+      <c r="J2" s="108">
         <v>8</v>
       </c>
-      <c r="K2" s="94">
+      <c r="K2" s="107">
         <f>SUM(L5:L32)</f>
         <v>13000</v>
       </c>
-      <c r="L2" s="94"/>
-      <c r="N2" s="95">
+      <c r="L2" s="107"/>
+      <c r="N2" s="108">
         <v>9</v>
       </c>
-      <c r="O2" s="94">
+      <c r="O2" s="107">
         <f>SUM(P5:P8)</f>
         <v>13000</v>
       </c>
-      <c r="P2" s="94"/>
-      <c r="R2" s="95">
+      <c r="P2" s="107"/>
+      <c r="R2" s="108">
         <v>11</v>
       </c>
-      <c r="S2" s="94">
+      <c r="S2" s="107">
         <f>SUM(T5:T35)</f>
         <v>13000</v>
       </c>
-      <c r="T2" s="94"/>
-      <c r="V2" s="95">
-        <v>12</v>
-      </c>
-      <c r="W2" s="94">
+      <c r="T2" s="107"/>
+      <c r="V2" s="108">
+        <v>12</v>
+      </c>
+      <c r="W2" s="107">
         <f>SUM(X5:X35)</f>
         <v>16500</v>
       </c>
-      <c r="X2" s="94"/>
-      <c r="Z2" s="95">
+      <c r="X2" s="107"/>
+      <c r="Z2" s="108">
         <v>1</v>
       </c>
-      <c r="AA2" s="94">
+      <c r="AA2" s="107">
         <f>SUM(AB5:AB35)</f>
         <v>16500</v>
       </c>
-      <c r="AB2" s="94"/>
-      <c r="AD2" s="95">
+      <c r="AB2" s="107"/>
+      <c r="AD2" s="108">
         <v>2</v>
       </c>
-      <c r="AE2" s="94">
+      <c r="AE2" s="107">
         <f>SUM(AF6:AF37)</f>
         <v>16500</v>
       </c>
-      <c r="AF2" s="94"/>
+      <c r="AF2" s="107"/>
     </row>
     <row r="3" spans="2:32" ht="24" customHeight="1">
-      <c r="B3" s="95"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="94"/>
-      <c r="F3" s="95"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="94"/>
-      <c r="J3" s="95"/>
-      <c r="K3" s="94"/>
-      <c r="L3" s="94"/>
-      <c r="N3" s="95"/>
-      <c r="O3" s="94"/>
-      <c r="P3" s="94"/>
-      <c r="R3" s="95"/>
-      <c r="S3" s="94"/>
-      <c r="T3" s="94"/>
-      <c r="V3" s="95"/>
-      <c r="W3" s="94"/>
-      <c r="X3" s="94"/>
-      <c r="Z3" s="95"/>
-      <c r="AA3" s="94"/>
-      <c r="AB3" s="94"/>
-      <c r="AD3" s="95"/>
-      <c r="AE3" s="94"/>
-      <c r="AF3" s="94"/>
+      <c r="B3" s="108"/>
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="107"/>
+      <c r="H3" s="107"/>
+      <c r="J3" s="108"/>
+      <c r="K3" s="107"/>
+      <c r="L3" s="107"/>
+      <c r="N3" s="108"/>
+      <c r="O3" s="107"/>
+      <c r="P3" s="107"/>
+      <c r="R3" s="108"/>
+      <c r="S3" s="107"/>
+      <c r="T3" s="107"/>
+      <c r="V3" s="108"/>
+      <c r="W3" s="107"/>
+      <c r="X3" s="107"/>
+      <c r="Z3" s="108"/>
+      <c r="AA3" s="107"/>
+      <c r="AB3" s="107"/>
+      <c r="AD3" s="108"/>
+      <c r="AE3" s="107"/>
+      <c r="AF3" s="107"/>
     </row>
     <row r="4" spans="2:32" ht="24" customHeight="1">
-      <c r="B4" s="95"/>
+      <c r="B4" s="108"/>
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="95"/>
+      <c r="F4" s="108"/>
       <c r="G4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="J4" s="95"/>
+      <c r="J4" s="108"/>
       <c r="K4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="N4" s="95"/>
+      <c r="N4" s="108"/>
       <c r="O4" s="6" t="s">
         <v>0</v>
       </c>
       <c r="P4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="R4" s="95"/>
+      <c r="R4" s="108"/>
       <c r="S4" s="18" t="s">
         <v>0</v>
       </c>
       <c r="T4" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="V4" s="95"/>
+      <c r="V4" s="108"/>
       <c r="W4" s="20" t="s">
         <v>0</v>
       </c>
       <c r="X4" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="Z4" s="95"/>
+      <c r="Z4" s="108"/>
       <c r="AA4" s="23" t="s">
         <v>0</v>
       </c>
       <c r="AB4" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="AD4" s="95"/>
+      <c r="AD4" s="108"/>
       <c r="AE4" s="41" t="s">
         <v>0</v>
       </c>
@@ -2919,14 +3017,14 @@
       <c r="L11" s="2">
         <v>100</v>
       </c>
-      <c r="N11" s="95">
+      <c r="N11" s="108">
         <v>10</v>
       </c>
-      <c r="O11" s="94">
+      <c r="O11" s="107">
         <f>SUM(P14:P44)</f>
         <v>13000</v>
       </c>
-      <c r="P11" s="94"/>
+      <c r="P11" s="107"/>
       <c r="R11" s="1">
         <v>45962</v>
       </c>
@@ -2989,9 +3087,9 @@
       <c r="L12" s="2">
         <v>100</v>
       </c>
-      <c r="N12" s="95"/>
-      <c r="O12" s="94"/>
-      <c r="P12" s="94"/>
+      <c r="N12" s="108"/>
+      <c r="O12" s="107"/>
+      <c r="P12" s="107"/>
       <c r="R12" s="1">
         <v>45963</v>
       </c>
@@ -3054,7 +3152,7 @@
       <c r="L13" s="2">
         <v>100</v>
       </c>
-      <c r="N13" s="95"/>
+      <c r="N13" s="108"/>
       <c r="O13" s="14" t="s">
         <v>0</v>
       </c>
@@ -4494,20 +4592,28 @@
       </c>
     </row>
     <row r="35" spans="2:32" ht="24" customHeight="1">
-      <c r="B35" s="95"/>
-      <c r="C35" s="94">
+      <c r="B35" s="108"/>
+      <c r="C35" s="107">
         <f>SUM(D38:D70)</f>
         <v>2750</v>
       </c>
-      <c r="D35" s="94"/>
-      <c r="F35" s="95">
+      <c r="D35" s="107"/>
+      <c r="F35" s="108">
         <v>3</v>
       </c>
-      <c r="G35" s="94">
+      <c r="G35" s="107">
         <f>SUM(H38:H73)</f>
-        <v>8600</v>
-      </c>
-      <c r="H35" s="94"/>
+        <v>16500</v>
+      </c>
+      <c r="H35" s="107"/>
+      <c r="J35" s="108">
+        <v>4</v>
+      </c>
+      <c r="K35" s="107">
+        <f>SUM(L38:L73)</f>
+        <v>850</v>
+      </c>
+      <c r="L35" s="107"/>
       <c r="N35" s="1">
         <v>45946</v>
       </c>
@@ -4528,12 +4634,15 @@
       </c>
     </row>
     <row r="36" spans="2:32" ht="24" customHeight="1">
-      <c r="B36" s="95"/>
-      <c r="C36" s="94"/>
-      <c r="D36" s="94"/>
-      <c r="F36" s="95"/>
-      <c r="G36" s="94"/>
-      <c r="H36" s="94"/>
+      <c r="B36" s="108"/>
+      <c r="C36" s="107"/>
+      <c r="D36" s="107"/>
+      <c r="F36" s="108"/>
+      <c r="G36" s="107"/>
+      <c r="H36" s="107"/>
+      <c r="J36" s="108"/>
+      <c r="K36" s="107"/>
+      <c r="L36" s="107"/>
       <c r="N36" s="1">
         <v>45947</v>
       </c>
@@ -4554,18 +4663,25 @@
       </c>
     </row>
     <row r="37" spans="2:32" ht="24" customHeight="1">
-      <c r="B37" s="95"/>
+      <c r="B37" s="108"/>
       <c r="C37" s="66" t="s">
         <v>0</v>
       </c>
       <c r="D37" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="F37" s="95"/>
+      <c r="F37" s="108"/>
       <c r="G37" s="73" t="s">
         <v>0</v>
       </c>
       <c r="H37" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="J37" s="108"/>
+      <c r="K37" s="94" t="s">
+        <v>0</v>
+      </c>
+      <c r="L37" s="94" t="s">
         <v>1</v>
       </c>
       <c r="N37" s="1">
@@ -4606,6 +4722,15 @@
       <c r="H38" s="2" t="s">
         <v>28</v>
       </c>
+      <c r="J38" s="97">
+        <v>46114</v>
+      </c>
+      <c r="K38" s="98" t="s">
+        <v>5</v>
+      </c>
+      <c r="L38" s="2">
+        <v>100</v>
+      </c>
       <c r="N38" s="1">
         <v>45949</v>
       </c>
@@ -4635,6 +4760,15 @@
       <c r="H39" s="2" t="s">
         <v>28</v>
       </c>
+      <c r="J39" s="97">
+        <v>46115</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="L39" s="2">
+        <v>150</v>
+      </c>
       <c r="N39" s="1">
         <v>45950</v>
       </c>
@@ -4664,6 +4798,15 @@
       <c r="H40" s="2">
         <v>200</v>
       </c>
+      <c r="J40" s="97">
+        <v>46116</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="N40" s="1">
         <v>45951</v>
       </c>
@@ -4693,6 +4836,15 @@
       <c r="H41" s="2">
         <v>100</v>
       </c>
+      <c r="J41" s="97">
+        <v>46117</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L41" s="2">
+        <v>300</v>
+      </c>
       <c r="N41" s="1">
         <v>45952</v>
       </c>
@@ -4722,6 +4874,15 @@
       <c r="H42" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="J42" s="97">
+        <v>46118</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L42" s="2">
+        <v>100</v>
+      </c>
       <c r="N42" s="1">
         <v>45953</v>
       </c>
@@ -4748,6 +4909,12 @@
       <c r="H43" s="2">
         <v>100</v>
       </c>
+      <c r="J43" s="97">
+        <v>46119</v>
+      </c>
+      <c r="L43" s="2">
+        <v>100</v>
+      </c>
       <c r="N43" s="1">
         <v>45954</v>
       </c>
@@ -4768,6 +4935,12 @@
       <c r="H44" s="2">
         <v>100</v>
       </c>
+      <c r="J44" s="97">
+        <v>46120</v>
+      </c>
+      <c r="L44" s="2">
+        <v>100</v>
+      </c>
       <c r="N44" s="1">
         <v>45955</v>
       </c>
@@ -4965,8 +5138,19 @@
         <v>1200</v>
       </c>
     </row>
+    <row r="62" spans="6:8" ht="24" customHeight="1">
+      <c r="F62" s="1">
+        <v>46114</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H62" s="2">
+        <v>7900</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="24">
     <mergeCell ref="AE2:AF3"/>
     <mergeCell ref="K2:L3"/>
     <mergeCell ref="R2:R4"/>
@@ -4989,6 +5173,8 @@
     <mergeCell ref="N11:N13"/>
     <mergeCell ref="F35:F37"/>
     <mergeCell ref="G35:H36"/>
+    <mergeCell ref="J35:J37"/>
+    <mergeCell ref="K35:L36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5004,40 +5190,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="24" customHeight="1">
-      <c r="B2" s="96">
+      <c r="B2" s="109">
         <v>11</v>
       </c>
-      <c r="C2" s="90">
+      <c r="C2" s="103">
         <f>SUM(D5:D31)</f>
         <v>2750</v>
       </c>
-      <c r="D2" s="90"/>
-      <c r="F2" s="96">
-        <v>12</v>
-      </c>
-      <c r="G2" s="90">
+      <c r="D2" s="103"/>
+      <c r="F2" s="109">
+        <v>12</v>
+      </c>
+      <c r="G2" s="103">
         <f>SUM(H5:H29)</f>
         <v>15470</v>
       </c>
-      <c r="H2" s="90"/>
+      <c r="H2" s="103"/>
     </row>
     <row r="3" spans="2:8" ht="24" customHeight="1">
-      <c r="B3" s="96"/>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="F3" s="96"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="103"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="103"/>
+      <c r="H3" s="103"/>
     </row>
     <row r="4" spans="2:8" ht="24" customHeight="1">
-      <c r="B4" s="96"/>
+      <c r="B4" s="109"/>
       <c r="C4" s="21" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="96"/>
+      <c r="F4" s="109"/>
       <c r="G4" s="21" t="s">
         <v>0</v>
       </c>
@@ -5402,91 +5588,110 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:Q38"/>
+  <dimension ref="B2:T38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="17.5703125" defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="16384" width="17.5703125" style="25"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" ht="24" customHeight="1">
-      <c r="B2" s="96">
-        <v>12</v>
-      </c>
-      <c r="C2" s="90">
+    <row r="2" spans="2:20" ht="24" customHeight="1">
+      <c r="B2" s="109">
+        <v>12</v>
+      </c>
+      <c r="C2" s="103">
         <f>SUM(D6:D39)</f>
         <v>8500</v>
       </c>
-      <c r="D2" s="90"/>
-      <c r="F2" s="96">
+      <c r="D2" s="103"/>
+      <c r="F2" s="109">
         <v>1</v>
       </c>
-      <c r="G2" s="90">
+      <c r="G2" s="103">
         <f>SUM(H5:H39)</f>
         <v>10500</v>
       </c>
-      <c r="H2" s="90"/>
-      <c r="J2" s="96">
+      <c r="H2" s="103"/>
+      <c r="J2" s="109">
         <v>2</v>
       </c>
-      <c r="K2" s="90">
+      <c r="K2" s="103">
         <f>SUM(L5:L39)</f>
         <v>10150</v>
       </c>
-      <c r="L2" s="90"/>
-      <c r="N2" s="96">
+      <c r="L2" s="103"/>
+      <c r="N2" s="110">
         <v>3</v>
       </c>
-      <c r="O2" s="90">
+      <c r="O2" s="103">
         <f>SUM(P5:P39)</f>
-        <v>2000</v>
-      </c>
-      <c r="P2" s="90"/>
-    </row>
-    <row r="3" spans="2:16" ht="24" customHeight="1">
-      <c r="B3" s="96"/>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="F3" s="96"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
-      <c r="J3" s="96"/>
-      <c r="K3" s="90"/>
-      <c r="L3" s="90"/>
-      <c r="N3" s="96"/>
-      <c r="O3" s="90"/>
-      <c r="P3" s="90"/>
-    </row>
-    <row r="4" spans="2:16" ht="24" customHeight="1">
-      <c r="B4" s="96"/>
+        <v>10500</v>
+      </c>
+      <c r="P2" s="103"/>
+      <c r="R2" s="110">
+        <v>4</v>
+      </c>
+      <c r="S2" s="103">
+        <f>SUM(T5:T39)</f>
+        <v>1350</v>
+      </c>
+      <c r="T2" s="103"/>
+    </row>
+    <row r="3" spans="2:20" ht="24" customHeight="1">
+      <c r="B3" s="109"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="103"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="103"/>
+      <c r="H3" s="103"/>
+      <c r="J3" s="109"/>
+      <c r="K3" s="103"/>
+      <c r="L3" s="103"/>
+      <c r="N3" s="111"/>
+      <c r="O3" s="103"/>
+      <c r="P3" s="103"/>
+      <c r="R3" s="111"/>
+      <c r="S3" s="103"/>
+      <c r="T3" s="103"/>
+    </row>
+    <row r="4" spans="2:20" ht="24" customHeight="1">
+      <c r="B4" s="109"/>
       <c r="C4" s="24" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="96"/>
+      <c r="F4" s="109"/>
       <c r="G4" s="24" t="s">
         <v>0</v>
       </c>
       <c r="H4" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="96"/>
+      <c r="J4" s="109"/>
       <c r="K4" s="45" t="s">
         <v>0</v>
       </c>
       <c r="L4" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="N4" s="96"/>
+      <c r="N4" s="112"/>
       <c r="O4" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="P4" s="71" t="s">
+      <c r="P4" s="90" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="2:16" ht="24" customHeight="1">
+      <c r="Q4" s="91"/>
+      <c r="R4" s="112"/>
+      <c r="S4" s="93" t="s">
+        <v>0</v>
+      </c>
+      <c r="T4" s="93" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="2:20" ht="24" customHeight="1">
       <c r="B5" s="4">
         <v>45992</v>
       </c>
@@ -5521,8 +5726,17 @@
       <c r="P5" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="6" spans="2:16" ht="24" customHeight="1">
+      <c r="R5" s="4">
+        <v>46114</v>
+      </c>
+      <c r="S5" s="95" t="s">
+        <v>5</v>
+      </c>
+      <c r="T5" s="25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="2:20" ht="24" customHeight="1">
       <c r="B6" s="4">
         <v>45993</v>
       </c>
@@ -5557,8 +5771,17 @@
       <c r="P6" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="7" spans="2:16" ht="24" customHeight="1">
+      <c r="R6" s="4">
+        <v>46115</v>
+      </c>
+      <c r="S6" s="96" t="s">
+        <v>5</v>
+      </c>
+      <c r="T6" s="25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="2:20" ht="24" customHeight="1">
       <c r="B7" s="4">
         <v>45994</v>
       </c>
@@ -5593,8 +5816,17 @@
       <c r="P7" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="8" spans="2:16" ht="24" customHeight="1">
+      <c r="R7" s="4">
+        <v>46116</v>
+      </c>
+      <c r="S7" s="99" t="s">
+        <v>33</v>
+      </c>
+      <c r="T7" s="99" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="2:20" ht="24" customHeight="1">
       <c r="B8" s="4">
         <v>45995</v>
       </c>
@@ -5632,8 +5864,17 @@
       <c r="P8" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="9" spans="2:16" ht="24" customHeight="1">
+      <c r="R8" s="4">
+        <v>46117</v>
+      </c>
+      <c r="S8" s="101" t="s">
+        <v>5</v>
+      </c>
+      <c r="T8" s="25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="2:20" ht="24" customHeight="1">
       <c r="B9" s="4">
         <v>45996</v>
       </c>
@@ -5671,8 +5912,17 @@
       <c r="P9" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="2:16" ht="24" customHeight="1">
+      <c r="R9" s="4">
+        <v>46118</v>
+      </c>
+      <c r="S9" s="83" t="s">
+        <v>32</v>
+      </c>
+      <c r="T9" s="83">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="10" spans="2:20" ht="24" customHeight="1">
       <c r="B10" s="4">
         <v>45997</v>
       </c>
@@ -5710,8 +5960,17 @@
       <c r="P10" s="76" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="11" spans="2:16" ht="24" customHeight="1">
+      <c r="R10" s="4">
+        <v>46119</v>
+      </c>
+      <c r="S10" s="83" t="s">
+        <v>32</v>
+      </c>
+      <c r="T10" s="83">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20" ht="24" customHeight="1">
       <c r="B11" s="4">
         <v>45998</v>
       </c>
@@ -5749,8 +6008,17 @@
       <c r="P11" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="12" spans="2:16" ht="24" customHeight="1">
+      <c r="R11" s="4">
+        <v>46120</v>
+      </c>
+      <c r="S11" s="83" t="s">
+        <v>32</v>
+      </c>
+      <c r="T11" s="83">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="12" spans="2:20" ht="24" customHeight="1">
       <c r="B12" s="4">
         <v>45999</v>
       </c>
@@ -5788,8 +6056,9 @@
       <c r="P12" s="77">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="2:16" ht="24" customHeight="1">
+      <c r="R12" s="91"/>
+    </row>
+    <row r="13" spans="2:20" ht="24" customHeight="1">
       <c r="B13" s="4">
         <v>46000</v>
       </c>
@@ -5827,8 +6096,9 @@
       <c r="P13" s="77">
         <v>100</v>
       </c>
-    </row>
-    <row r="14" spans="2:16" ht="24" customHeight="1">
+      <c r="R13" s="91"/>
+    </row>
+    <row r="14" spans="2:20" ht="24" customHeight="1">
       <c r="B14" s="4">
         <v>46001</v>
       </c>
@@ -5866,8 +6136,9 @@
       <c r="P14" s="77" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="15" spans="2:16" ht="24" customHeight="1">
+      <c r="R14" s="91"/>
+    </row>
+    <row r="15" spans="2:20" ht="24" customHeight="1">
       <c r="B15" s="4">
         <v>46002</v>
       </c>
@@ -5905,8 +6176,9 @@
       <c r="P15" s="77" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="16" spans="2:16" ht="24" customHeight="1">
+      <c r="R15" s="91"/>
+    </row>
+    <row r="16" spans="2:20" ht="24" customHeight="1">
       <c r="B16" s="4">
         <v>46003</v>
       </c>
@@ -5944,8 +6216,9 @@
       <c r="P16" s="77" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="17" spans="2:17" ht="24" customHeight="1">
+      <c r="R16" s="91"/>
+    </row>
+    <row r="17" spans="2:18" ht="24" customHeight="1">
       <c r="B17" s="4">
         <v>46004</v>
       </c>
@@ -5983,8 +6256,9 @@
       <c r="P17" s="78" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="18" spans="2:17" ht="24" customHeight="1">
+      <c r="R17" s="91"/>
+    </row>
+    <row r="18" spans="2:18" ht="24" customHeight="1">
       <c r="B18" s="4">
         <v>46005</v>
       </c>
@@ -6022,8 +6296,9 @@
       <c r="P18" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="19" spans="2:17" ht="24" customHeight="1">
+      <c r="R18" s="91"/>
+    </row>
+    <row r="19" spans="2:18" ht="24" customHeight="1">
       <c r="B19" s="4">
         <v>46006</v>
       </c>
@@ -6061,8 +6336,9 @@
       <c r="P19" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="20" spans="2:17" ht="24" customHeight="1">
+      <c r="R19" s="91"/>
+    </row>
+    <row r="20" spans="2:18" ht="24" customHeight="1">
       <c r="B20" s="4">
         <v>46007</v>
       </c>
@@ -6100,8 +6376,9 @@
       <c r="P20" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="2:17" ht="24" customHeight="1">
+      <c r="R20" s="91"/>
+    </row>
+    <row r="21" spans="2:18" ht="24" customHeight="1">
       <c r="B21" s="4">
         <v>46008</v>
       </c>
@@ -6139,8 +6416,9 @@
       <c r="P21" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="22" spans="2:17" ht="24" customHeight="1">
+      <c r="R21" s="91"/>
+    </row>
+    <row r="22" spans="2:18" ht="24" customHeight="1">
       <c r="B22" s="4">
         <v>46009</v>
       </c>
@@ -6178,8 +6456,9 @@
       <c r="P22" s="80">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="2:17" ht="24" customHeight="1">
+      <c r="R22" s="91"/>
+    </row>
+    <row r="23" spans="2:18" ht="24" customHeight="1">
       <c r="B23" s="4">
         <v>46010</v>
       </c>
@@ -6217,8 +6496,9 @@
       <c r="P23" s="80">
         <v>100</v>
       </c>
-    </row>
-    <row r="24" spans="2:17" ht="24" customHeight="1">
+      <c r="R23" s="91"/>
+    </row>
+    <row r="24" spans="2:18" ht="24" customHeight="1">
       <c r="B24" s="4">
         <v>46011</v>
       </c>
@@ -6256,8 +6536,9 @@
       <c r="P24" s="81" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="25" spans="2:17" ht="24" customHeight="1">
+      <c r="R24" s="91"/>
+    </row>
+    <row r="25" spans="2:18" ht="24" customHeight="1">
       <c r="B25" s="4">
         <v>46012</v>
       </c>
@@ -6295,8 +6576,9 @@
       <c r="P25" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="26" spans="2:17" ht="24" customHeight="1">
+      <c r="R25" s="91"/>
+    </row>
+    <row r="26" spans="2:18" ht="24" customHeight="1">
       <c r="B26" s="4">
         <v>46013</v>
       </c>
@@ -6329,16 +6611,15 @@
         <v>46104</v>
       </c>
       <c r="O26" s="83" t="s">
-        <v>28</v>
-      </c>
-      <c r="P26" s="83" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q26" s="83">
-        <v>-350</v>
-      </c>
-    </row>
-    <row r="27" spans="2:17" ht="24" customHeight="1">
+        <v>32</v>
+      </c>
+      <c r="P26" s="83">
+        <v>350</v>
+      </c>
+      <c r="Q26" s="83"/>
+      <c r="R26" s="91"/>
+    </row>
+    <row r="27" spans="2:18" ht="24" customHeight="1">
       <c r="B27" s="4">
         <v>46014</v>
       </c>
@@ -6376,8 +6657,9 @@
       <c r="P27" s="82">
         <v>100</v>
       </c>
-    </row>
-    <row r="28" spans="2:17" ht="24" customHeight="1">
+      <c r="R27" s="91"/>
+    </row>
+    <row r="28" spans="2:18" ht="24" customHeight="1">
       <c r="B28" s="4">
         <v>46015</v>
       </c>
@@ -6415,8 +6697,9 @@
       <c r="P28" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="29" spans="2:17" ht="24" customHeight="1">
+      <c r="R28" s="91"/>
+    </row>
+    <row r="29" spans="2:18" ht="24" customHeight="1">
       <c r="B29" s="4">
         <v>46016</v>
       </c>
@@ -6454,8 +6737,9 @@
       <c r="P29" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="30" spans="2:17" ht="24" customHeight="1">
+      <c r="R29" s="91"/>
+    </row>
+    <row r="30" spans="2:18" ht="24" customHeight="1">
       <c r="B30" s="4">
         <v>46017</v>
       </c>
@@ -6493,8 +6777,9 @@
       <c r="P30" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="31" spans="2:17" ht="24" customHeight="1">
+      <c r="R30" s="91"/>
+    </row>
+    <row r="31" spans="2:18" ht="24" customHeight="1">
       <c r="B31" s="4">
         <v>46018</v>
       </c>
@@ -6532,8 +6817,9 @@
       <c r="P31" s="86" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="32" spans="2:17" ht="24" customHeight="1">
+      <c r="R31" s="91"/>
+    </row>
+    <row r="32" spans="2:18" ht="24" customHeight="1">
       <c r="B32" s="4">
         <v>46019</v>
       </c>
@@ -6567,8 +6853,9 @@
       <c r="P32" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="33" spans="2:8" ht="24" customHeight="1">
+      <c r="R32" s="91"/>
+    </row>
+    <row r="33" spans="2:18" ht="24" customHeight="1">
       <c r="B33" s="4">
         <v>46020</v>
       </c>
@@ -6587,8 +6874,18 @@
       <c r="H33" s="44" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="34" spans="2:8" ht="24" customHeight="1">
+      <c r="N33" s="4">
+        <v>46111</v>
+      </c>
+      <c r="O33" s="91" t="s">
+        <v>5</v>
+      </c>
+      <c r="P33" s="91">
+        <v>100</v>
+      </c>
+      <c r="R33" s="91"/>
+    </row>
+    <row r="34" spans="2:18" ht="24" customHeight="1">
       <c r="B34" s="4">
         <v>46021</v>
       </c>
@@ -6607,8 +6904,18 @@
       <c r="H34" s="44">
         <v>100</v>
       </c>
-    </row>
-    <row r="35" spans="2:8" ht="24" customHeight="1">
+      <c r="N34" s="4">
+        <v>46112</v>
+      </c>
+      <c r="O34" s="91" t="s">
+        <v>5</v>
+      </c>
+      <c r="P34" s="91">
+        <v>100</v>
+      </c>
+      <c r="R34" s="91"/>
+    </row>
+    <row r="35" spans="2:18" ht="24" customHeight="1">
       <c r="B35" s="4">
         <v>46022</v>
       </c>
@@ -6627,8 +6934,12 @@
       <c r="H35" s="44">
         <v>100</v>
       </c>
-    </row>
-    <row r="36" spans="2:8" ht="24" customHeight="1">
+      <c r="N35" s="4">
+        <v>46113</v>
+      </c>
+      <c r="R35" s="91"/>
+    </row>
+    <row r="36" spans="2:18" ht="24" customHeight="1">
       <c r="B36" s="4">
         <v>46023</v>
       </c>
@@ -6647,8 +6958,15 @@
       <c r="H36" s="25">
         <v>7800</v>
       </c>
-    </row>
-    <row r="37" spans="2:8" ht="24" customHeight="1">
+      <c r="N36" s="4">
+        <v>46114</v>
+      </c>
+      <c r="O36" s="95"/>
+      <c r="P36" s="25">
+        <v>7950</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" ht="24" customHeight="1">
       <c r="B37" s="4">
         <v>46024</v>
       </c>
@@ -6659,7 +6977,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="2:8" ht="24" customHeight="1">
+    <row r="38" spans="2:18" ht="24" customHeight="1">
       <c r="B38" s="4">
         <v>46025</v>
       </c>
@@ -6671,15 +6989,17 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="N2:N4"/>
-    <mergeCell ref="O2:P3"/>
-    <mergeCell ref="K2:L3"/>
+  <mergeCells count="10">
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="C2:D3"/>
     <mergeCell ref="F2:F4"/>
     <mergeCell ref="G2:H3"/>
     <mergeCell ref="J2:J4"/>
+    <mergeCell ref="R2:R4"/>
+    <mergeCell ref="S2:T3"/>
+    <mergeCell ref="N2:N4"/>
+    <mergeCell ref="O2:P3"/>
+    <mergeCell ref="K2:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6688,85 +7008,103 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:Q36"/>
+  <dimension ref="A2:U36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="17.5703125" defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="16384" width="17.5703125" style="29"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:17" ht="24" customHeight="1">
-      <c r="B2" s="96"/>
-      <c r="C2" s="90">
+    <row r="2" spans="1:21" ht="24" customHeight="1">
+      <c r="B2" s="109"/>
+      <c r="C2" s="103">
         <f>SUM(D5:D44)</f>
         <v>10500</v>
       </c>
-      <c r="D2" s="90"/>
-      <c r="F2" s="96"/>
-      <c r="G2" s="90">
+      <c r="D2" s="103"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="103">
         <f>SUM(H5:H44)</f>
         <v>10500</v>
       </c>
-      <c r="H2" s="90"/>
-      <c r="K2" s="96"/>
-      <c r="L2" s="90">
+      <c r="H2" s="103"/>
+      <c r="K2" s="109"/>
+      <c r="L2" s="103">
         <f>SUM(M5:M37)</f>
         <v>5250</v>
       </c>
-      <c r="M2" s="90"/>
-      <c r="O2" s="96">
+      <c r="M2" s="103"/>
+      <c r="O2" s="109">
         <v>3</v>
       </c>
-      <c r="P2" s="90">
+      <c r="P2" s="103">
         <f>SUM(Q5:Q37)</f>
-        <v>360</v>
-      </c>
-      <c r="Q2" s="90"/>
-    </row>
-    <row r="3" spans="1:17" ht="24" customHeight="1">
-      <c r="B3" s="96"/>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="F3" s="96"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
-      <c r="K3" s="96"/>
-      <c r="L3" s="90"/>
-      <c r="M3" s="90"/>
-      <c r="O3" s="96"/>
-      <c r="P3" s="90"/>
-      <c r="Q3" s="90"/>
-    </row>
-    <row r="4" spans="1:17" ht="24" customHeight="1">
-      <c r="B4" s="96"/>
+        <v>10500</v>
+      </c>
+      <c r="Q2" s="103"/>
+      <c r="S2" s="109">
+        <v>4</v>
+      </c>
+      <c r="T2" s="103">
+        <f>SUM(U5:U37)</f>
+        <v>530</v>
+      </c>
+      <c r="U2" s="103"/>
+    </row>
+    <row r="3" spans="1:21" ht="24" customHeight="1">
+      <c r="B3" s="109"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="103"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="103"/>
+      <c r="H3" s="103"/>
+      <c r="K3" s="109"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="103"/>
+      <c r="O3" s="109"/>
+      <c r="P3" s="103"/>
+      <c r="Q3" s="103"/>
+      <c r="S3" s="109"/>
+      <c r="T3" s="103"/>
+      <c r="U3" s="103"/>
+    </row>
+    <row r="4" spans="1:21" ht="24" customHeight="1">
+      <c r="B4" s="109"/>
       <c r="C4" s="28" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="96"/>
+      <c r="F4" s="109"/>
       <c r="G4" s="33" t="s">
         <v>0</v>
       </c>
       <c r="H4" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="96"/>
+      <c r="K4" s="109"/>
       <c r="L4" s="57" t="s">
         <v>0</v>
       </c>
       <c r="M4" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="O4" s="96"/>
+      <c r="O4" s="109"/>
       <c r="P4" s="71" t="s">
         <v>0</v>
       </c>
       <c r="Q4" s="71" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" ht="24" customHeight="1">
+      <c r="S4" s="109"/>
+      <c r="T4" s="93" t="s">
+        <v>0</v>
+      </c>
+      <c r="U4" s="93" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="24" customHeight="1">
       <c r="B5" s="31">
         <v>46006</v>
       </c>
@@ -6803,8 +7141,17 @@
       <c r="Q5" s="72" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" ht="24" customHeight="1">
+      <c r="S5" s="4">
+        <v>46114</v>
+      </c>
+      <c r="T5" s="95" t="s">
+        <v>5</v>
+      </c>
+      <c r="U5" s="29">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="24" customHeight="1">
       <c r="A6" s="30"/>
       <c r="B6" s="31">
         <v>46007</v>
@@ -6843,8 +7190,17 @@
       <c r="Q6" s="29">
         <v>60</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" ht="24" customHeight="1">
+      <c r="S6" s="4">
+        <v>46115</v>
+      </c>
+      <c r="T6" s="96" t="s">
+        <v>33</v>
+      </c>
+      <c r="U6" s="96" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="24" customHeight="1">
       <c r="A7" s="30"/>
       <c r="B7" s="31">
         <v>46008</v>
@@ -6883,8 +7239,17 @@
       <c r="Q7" s="82">
         <v>60</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" ht="24" customHeight="1">
+      <c r="S7" s="4">
+        <v>46116</v>
+      </c>
+      <c r="T7" s="83" t="s">
+        <v>32</v>
+      </c>
+      <c r="U7" s="83">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="24" customHeight="1">
       <c r="A8" s="30"/>
       <c r="B8" s="31">
         <v>46009</v>
@@ -6923,8 +7288,17 @@
       <c r="Q8" s="82">
         <v>60</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" ht="24" customHeight="1">
+      <c r="S8" s="4">
+        <v>46117</v>
+      </c>
+      <c r="T8" s="100" t="s">
+        <v>5</v>
+      </c>
+      <c r="U8" s="29">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="24" customHeight="1">
       <c r="A9" s="30"/>
       <c r="B9" s="31">
         <v>46010</v>
@@ -6963,8 +7337,17 @@
       <c r="Q9" s="75">
         <v>60</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" ht="24" customHeight="1">
+      <c r="S9" s="4">
+        <v>46118</v>
+      </c>
+      <c r="T9" s="101" t="s">
+        <v>5</v>
+      </c>
+      <c r="U9" s="101">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="24" customHeight="1">
       <c r="A10" s="30"/>
       <c r="B10" s="31">
         <v>46011</v>
@@ -7004,7 +7387,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="24" customHeight="1">
+    <row r="11" spans="1:21" ht="24" customHeight="1">
       <c r="A11" s="30"/>
       <c r="B11" s="31">
         <v>46012</v>
@@ -7044,7 +7427,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="24" customHeight="1">
+    <row r="12" spans="1:21" ht="24" customHeight="1">
       <c r="A12" s="30"/>
       <c r="B12" s="31">
         <v>46013</v>
@@ -7084,7 +7467,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="24" customHeight="1">
+    <row r="13" spans="1:21" ht="24" customHeight="1">
       <c r="A13" s="30"/>
       <c r="B13" s="31">
         <v>46014</v>
@@ -7114,11 +7497,17 @@
         <v>60</v>
       </c>
       <c r="N13" s="70"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="77"/>
-      <c r="Q13" s="77"/>
-    </row>
-    <row r="14" spans="1:17" ht="24" customHeight="1">
+      <c r="O13" s="4">
+        <v>46111</v>
+      </c>
+      <c r="P13" s="89" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q13" s="77">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="24" customHeight="1">
       <c r="A14" s="30"/>
       <c r="B14" s="31">
         <v>46015</v>
@@ -7148,11 +7537,17 @@
         <v>60</v>
       </c>
       <c r="N14" s="70"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="77"/>
-      <c r="Q14" s="77"/>
-    </row>
-    <row r="15" spans="1:17" ht="24" customHeight="1">
+      <c r="O14" s="4">
+        <v>46112</v>
+      </c>
+      <c r="P14" s="91" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="77">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="24" customHeight="1">
       <c r="A15" s="30"/>
       <c r="B15" s="31">
         <v>46016</v>
@@ -7182,11 +7577,17 @@
         <v>60</v>
       </c>
       <c r="N15" s="70"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="77"/>
-      <c r="Q15" s="77"/>
-    </row>
-    <row r="16" spans="1:17" ht="24" customHeight="1">
+      <c r="O15" s="4">
+        <v>46113</v>
+      </c>
+      <c r="P15" s="91" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="77">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="24" customHeight="1">
       <c r="A16" s="30"/>
       <c r="B16" s="31">
         <v>46017</v>
@@ -7216,9 +7617,15 @@
         <v>28</v>
       </c>
       <c r="N16" s="70"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="77"/>
-      <c r="Q16" s="77"/>
+      <c r="O16" s="4">
+        <v>46114</v>
+      </c>
+      <c r="P16" s="92" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q16" s="77">
+        <v>9960</v>
+      </c>
     </row>
     <row r="17" spans="1:17" ht="21">
       <c r="A17" s="30"/>
@@ -7363,7 +7770,7 @@
       <c r="H21" s="44">
         <v>60</v>
       </c>
-      <c r="I21" s="97"/>
+      <c r="I21" s="113"/>
     </row>
     <row r="22" spans="1:17" ht="21">
       <c r="A22" s="30"/>
@@ -7385,7 +7792,7 @@
       <c r="H22" s="44">
         <v>60</v>
       </c>
-      <c r="I22" s="97"/>
+      <c r="I22" s="113"/>
     </row>
     <row r="23" spans="1:17" ht="21">
       <c r="A23" s="30"/>
@@ -7681,16 +8088,18 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="O2:O4"/>
-    <mergeCell ref="P2:Q3"/>
-    <mergeCell ref="L2:M3"/>
+  <mergeCells count="11">
+    <mergeCell ref="K2:K4"/>
     <mergeCell ref="I21:I22"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="C2:D3"/>
     <mergeCell ref="F2:F4"/>
     <mergeCell ref="G2:H3"/>
-    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="S2:S4"/>
+    <mergeCell ref="T2:U3"/>
+    <mergeCell ref="O2:O4"/>
+    <mergeCell ref="P2:Q3"/>
+    <mergeCell ref="L2:M3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
